--- a/research/traditional_assets/database/data/iceland/iceland_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_retail_automotive.xlsx
@@ -1267,7 +1267,7 @@
         <v>1.42456140350877</v>
       </c>
       <c r="F2">
-        <v>4.60701007300386</v>
+        <v>4.60701007300385</v>
       </c>
       <c r="G2">
         <v>4.41192052980132</v>
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08326797296801991</v>
+        <v>0.08313743702208387</v>
       </c>
       <c r="C2">
-        <v>919.563432959186</v>
+        <v>912.8943562582454</v>
       </c>
       <c r="D2">
-        <v>874.663432959186</v>
+        <v>877.7213562582454</v>
       </c>
       <c r="E2">
-        <v>-333.1</v>
+        <v>-323.373</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.727</v>
       </c>
       <c r="G2">
         <v>44.9</v>
@@ -1585,28 +1585,28 @@
         <v>59.475</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4892681</v>
       </c>
       <c r="N2">
-        <v>59.475</v>
+        <v>58.9857319</v>
       </c>
       <c r="O2">
-        <v>11.895</v>
+        <v>11.79714638</v>
       </c>
       <c r="P2">
-        <v>47.58</v>
+        <v>47.18858552</v>
       </c>
       <c r="Q2">
-        <v>82.47999999999999</v>
+        <v>82.08858552000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08326797296801991</v>
+        <v>0.08357074446675139</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307606</v>
+        <v>0.7164970653807062</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>121.559120653891</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08313743702208387</v>
+        <v>0.08300690107614783</v>
       </c>
       <c r="C3">
-        <v>912.8943562582454</v>
+        <v>906.2467362709194</v>
       </c>
       <c r="D3">
-        <v>877.7213562582454</v>
+        <v>880.8007362709194</v>
       </c>
       <c r="E3">
-        <v>-323.373</v>
+        <v>-313.646</v>
       </c>
       <c r="F3">
-        <v>9.727</v>
+        <v>19.454</v>
       </c>
       <c r="G3">
         <v>44.9</v>
@@ -1667,28 +1667,28 @@
         <v>59.475</v>
       </c>
       <c r="M3">
-        <v>0.4892681</v>
+        <v>0.9785362</v>
       </c>
       <c r="N3">
-        <v>58.9857319</v>
+        <v>58.4964638</v>
       </c>
       <c r="O3">
-        <v>11.79714638</v>
+        <v>11.69929276</v>
       </c>
       <c r="P3">
-        <v>47.18858552</v>
+        <v>46.79717104</v>
       </c>
       <c r="Q3">
-        <v>82.08858552000001</v>
+        <v>81.69717104</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08357074446675139</v>
+        <v>0.08387969497566106</v>
       </c>
       <c r="T3">
-        <v>0.7164970653807062</v>
+        <v>0.7223577423704465</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>121.559120653891</v>
+        <v>60.77956032694549</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08300690107614783</v>
+        <v>0.08287636513021179</v>
       </c>
       <c r="C4">
-        <v>906.2467362709194</v>
+        <v>899.6207996272243</v>
       </c>
       <c r="D4">
-        <v>880.8007362709194</v>
+        <v>883.9017996272244</v>
       </c>
       <c r="E4">
-        <v>-313.646</v>
+        <v>-303.919</v>
       </c>
       <c r="F4">
-        <v>19.454</v>
+        <v>29.181</v>
       </c>
       <c r="G4">
         <v>44.9</v>
@@ -1749,28 +1749,28 @@
         <v>59.475</v>
       </c>
       <c r="M4">
-        <v>0.9785362</v>
+        <v>1.4678043</v>
       </c>
       <c r="N4">
-        <v>58.4964638</v>
+        <v>58.0071957</v>
       </c>
       <c r="O4">
-        <v>11.69929276</v>
+        <v>11.60143914</v>
       </c>
       <c r="P4">
-        <v>46.79717104</v>
+        <v>46.40575656</v>
       </c>
       <c r="Q4">
-        <v>81.69717104</v>
+        <v>81.30575655999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08387969497566106</v>
+        <v>0.08419501559815648</v>
       </c>
       <c r="T4">
-        <v>0.7223577423704465</v>
+        <v>0.7283392580610062</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.77956032694549</v>
+        <v>40.51970688463033</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08287636513021179</v>
+        <v>0.08274582918427575</v>
       </c>
       <c r="C5">
-        <v>899.6207996272243</v>
+        <v>893.016776160067</v>
       </c>
       <c r="D5">
-        <v>883.9017996272244</v>
+        <v>887.0247761600671</v>
       </c>
       <c r="E5">
-        <v>-303.919</v>
+        <v>-294.192</v>
       </c>
       <c r="F5">
-        <v>29.181</v>
+        <v>38.908</v>
       </c>
       <c r="G5">
         <v>44.9</v>
@@ -1831,28 +1831,28 @@
         <v>59.475</v>
       </c>
       <c r="M5">
-        <v>1.4678043</v>
+        <v>1.9570724</v>
       </c>
       <c r="N5">
-        <v>58.0071957</v>
+        <v>57.5179276</v>
       </c>
       <c r="O5">
-        <v>11.60143914</v>
+        <v>11.50358552</v>
       </c>
       <c r="P5">
-        <v>46.40575656</v>
+        <v>46.01434208</v>
       </c>
       <c r="Q5">
-        <v>81.30575655999999</v>
+        <v>80.91434208</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08419501559815648</v>
+        <v>0.08451690540028725</v>
       </c>
       <c r="T5">
-        <v>0.7283392580610062</v>
+        <v>0.7344453886617861</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.51970688463033</v>
+        <v>30.38978016347275</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08274582918427575</v>
+        <v>0.08261529323833972</v>
       </c>
       <c r="C6">
-        <v>893.016776160067</v>
+        <v>886.4348989620274</v>
       </c>
       <c r="D6">
-        <v>887.0247761600671</v>
+        <v>890.1698989620274</v>
       </c>
       <c r="E6">
-        <v>-294.192</v>
+        <v>-284.465</v>
       </c>
       <c r="F6">
-        <v>38.908</v>
+        <v>48.63500000000001</v>
       </c>
       <c r="G6">
         <v>44.9</v>
@@ -1913,28 +1913,28 @@
         <v>59.475</v>
       </c>
       <c r="M6">
-        <v>1.9570724</v>
+        <v>2.4463405</v>
       </c>
       <c r="N6">
-        <v>57.5179276</v>
+        <v>57.0286595</v>
       </c>
       <c r="O6">
-        <v>11.50358552</v>
+        <v>11.4057319</v>
       </c>
       <c r="P6">
-        <v>46.01434208</v>
+        <v>45.6229276</v>
       </c>
       <c r="Q6">
-        <v>80.91434208</v>
+        <v>80.5229276</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08451690540028725</v>
+        <v>0.08484557182983128</v>
       </c>
       <c r="T6">
-        <v>0.7344453886617861</v>
+        <v>0.7406800693804768</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.38978016347275</v>
+        <v>24.3118241307782</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08261529323833972</v>
+        <v>0.08248475729240368</v>
       </c>
       <c r="C7">
-        <v>886.4348989620274</v>
+        <v>879.8754044433533</v>
       </c>
       <c r="D7">
-        <v>890.1698989620274</v>
+        <v>893.3374044433533</v>
       </c>
       <c r="E7">
-        <v>-284.465</v>
+        <v>-274.738</v>
       </c>
       <c r="F7">
-        <v>48.63500000000001</v>
+        <v>58.36200000000001</v>
       </c>
       <c r="G7">
         <v>44.9</v>
@@ -1995,28 +1995,28 @@
         <v>59.475</v>
       </c>
       <c r="M7">
-        <v>2.4463405</v>
+        <v>2.9356086</v>
       </c>
       <c r="N7">
-        <v>57.0286595</v>
+        <v>56.5393914</v>
       </c>
       <c r="O7">
-        <v>11.4057319</v>
+        <v>11.30787828</v>
       </c>
       <c r="P7">
-        <v>45.6229276</v>
+        <v>45.23151312</v>
       </c>
       <c r="Q7">
-        <v>80.5229276</v>
+        <v>80.13151311999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08484557182983128</v>
+        <v>0.08518123116213158</v>
       </c>
       <c r="T7">
-        <v>0.7406800693804768</v>
+        <v>0.7470474028804166</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.3118241307782</v>
+        <v>20.25985344231516</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08248475729240368</v>
+        <v>0.08235422134646765</v>
       </c>
       <c r="C8">
-        <v>879.8754044433533</v>
+        <v>873.3385323911973</v>
       </c>
       <c r="D8">
-        <v>893.3374044433533</v>
+        <v>896.5275323911974</v>
       </c>
       <c r="E8">
-        <v>-274.738</v>
+        <v>-265.011</v>
       </c>
       <c r="F8">
-        <v>58.362</v>
+        <v>68.089</v>
       </c>
       <c r="G8">
         <v>44.9</v>
@@ -2077,28 +2077,28 @@
         <v>59.475</v>
       </c>
       <c r="M8">
-        <v>2.9356086</v>
+        <v>3.4248767</v>
       </c>
       <c r="N8">
-        <v>56.5393914</v>
+        <v>56.0501233</v>
       </c>
       <c r="O8">
-        <v>11.30787828</v>
+        <v>11.21002466</v>
       </c>
       <c r="P8">
-        <v>45.23151312</v>
+        <v>44.84009864</v>
       </c>
       <c r="Q8">
-        <v>80.13151311999999</v>
+        <v>79.74009864</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08518123116213158</v>
+        <v>0.08552410897469639</v>
       </c>
       <c r="T8">
-        <v>0.7470474028804166</v>
+        <v>0.7535516682835807</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.25985344231516</v>
+        <v>17.36558866484157</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08235422134646764</v>
+        <v>0.08222368540053161</v>
       </c>
       <c r="C9">
-        <v>873.3385323911976</v>
+        <v>866.8245260301298</v>
       </c>
       <c r="D9">
-        <v>896.5275323911977</v>
+        <v>899.7405260301299</v>
       </c>
       <c r="E9">
-        <v>-265.011</v>
+        <v>-255.284</v>
       </c>
       <c r="F9">
-        <v>68.08900000000001</v>
+        <v>77.816</v>
       </c>
       <c r="G9">
         <v>44.9</v>
@@ -2159,28 +2159,28 @@
         <v>59.475</v>
       </c>
       <c r="M9">
-        <v>3.4248767</v>
+        <v>3.9141448</v>
       </c>
       <c r="N9">
-        <v>56.0501233</v>
+        <v>55.5608552</v>
       </c>
       <c r="O9">
-        <v>11.21002466</v>
+        <v>11.11217104</v>
       </c>
       <c r="P9">
-        <v>44.84009864</v>
+        <v>44.44868416</v>
       </c>
       <c r="Q9">
-        <v>79.74009864</v>
+        <v>79.34868416</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08552410897469639</v>
+        <v>0.08587444065275174</v>
       </c>
       <c r="T9">
-        <v>0.7535516682835807</v>
+        <v>0.7601973307607266</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.36558866484157</v>
+        <v>15.19489008173637</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08222368540053161</v>
+        <v>0.08209314945459557</v>
       </c>
       <c r="C10">
-        <v>866.8245260301298</v>
+        <v>860.3336320839533</v>
       </c>
       <c r="D10">
-        <v>899.7405260301299</v>
+        <v>902.9766320839533</v>
       </c>
       <c r="E10">
-        <v>-255.284</v>
+        <v>-245.557</v>
       </c>
       <c r="F10">
-        <v>77.816</v>
+        <v>87.54300000000001</v>
       </c>
       <c r="G10">
         <v>44.9</v>
@@ -2241,28 +2241,28 @@
         <v>59.475</v>
       </c>
       <c r="M10">
-        <v>3.9141448</v>
+        <v>4.4034129</v>
       </c>
       <c r="N10">
-        <v>55.5608552</v>
+        <v>55.0715871</v>
       </c>
       <c r="O10">
-        <v>11.11217104</v>
+        <v>11.01431742</v>
       </c>
       <c r="P10">
-        <v>44.44868416</v>
+        <v>44.05726968</v>
       </c>
       <c r="Q10">
-        <v>79.34868416</v>
+        <v>78.95726968</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08587444065275174</v>
+        <v>0.086232471928127</v>
       </c>
       <c r="T10">
-        <v>0.7601973307607266</v>
+        <v>0.7669890517538538</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.19489008173637</v>
+        <v>13.50656896154344</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08209314945459557</v>
+        <v>0.08208261350865952</v>
       </c>
       <c r="C11">
-        <v>860.3336320839533</v>
+        <v>850.8688434314046</v>
       </c>
       <c r="D11">
-        <v>902.9766320839533</v>
+        <v>903.2388434314046</v>
       </c>
       <c r="E11">
-        <v>-245.557</v>
+        <v>-235.83</v>
       </c>
       <c r="F11">
-        <v>87.54300000000001</v>
+        <v>97.27</v>
       </c>
       <c r="G11">
         <v>44.9</v>
@@ -2323,45 +2323,45 @@
         <v>59.475</v>
       </c>
       <c r="M11">
-        <v>4.4034129</v>
+        <v>5.038586</v>
       </c>
       <c r="N11">
-        <v>55.0715871</v>
+        <v>54.436414</v>
       </c>
       <c r="O11">
-        <v>11.01431742</v>
+        <v>10.8872828</v>
       </c>
       <c r="P11">
-        <v>44.05726968</v>
+        <v>43.5491312</v>
       </c>
       <c r="Q11">
-        <v>78.95726968</v>
+        <v>78.4491312</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.086232471928127</v>
+        <v>0.08659845945406613</v>
       </c>
       <c r="T11">
-        <v>0.7669890517538538</v>
+        <v>0.7739316998801615</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.50656896154344</v>
+        <v>11.80390688975042</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08208261350865952</v>
+        <v>0.08196407756272348</v>
       </c>
       <c r="C12">
-        <v>850.8688434314046</v>
+        <v>844.1024130885904</v>
       </c>
       <c r="D12">
-        <v>903.2388434314046</v>
+        <v>906.1994130885904</v>
       </c>
       <c r="E12">
-        <v>-235.83</v>
+        <v>-226.103</v>
       </c>
       <c r="F12">
-        <v>97.27000000000001</v>
+        <v>106.997</v>
       </c>
       <c r="G12">
         <v>44.9</v>
@@ -2405,28 +2405,28 @@
         <v>59.475</v>
       </c>
       <c r="M12">
-        <v>5.038586</v>
+        <v>5.5424446</v>
       </c>
       <c r="N12">
-        <v>54.436414</v>
+        <v>53.9325554</v>
       </c>
       <c r="O12">
-        <v>10.8872828</v>
+        <v>10.78651108</v>
       </c>
       <c r="P12">
-        <v>43.5491312</v>
+        <v>43.14604432</v>
       </c>
       <c r="Q12">
-        <v>78.4491312</v>
+        <v>78.04604431999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08659845945406613</v>
+        <v>0.08697267141879042</v>
       </c>
       <c r="T12">
-        <v>0.7739316998801616</v>
+        <v>0.7810303625711055</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.80390688975042</v>
+        <v>10.73082444522765</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08196407756272348</v>
+        <v>0.08184554161678745</v>
       </c>
       <c r="C13">
-        <v>844.1024130885904</v>
+        <v>837.3554544423621</v>
       </c>
       <c r="D13">
-        <v>906.1994130885904</v>
+        <v>909.1794544423622</v>
       </c>
       <c r="E13">
-        <v>-226.103</v>
+        <v>-216.376</v>
       </c>
       <c r="F13">
-        <v>106.997</v>
+        <v>116.724</v>
       </c>
       <c r="G13">
         <v>44.9</v>
@@ -2487,28 +2487,28 @@
         <v>59.475</v>
       </c>
       <c r="M13">
-        <v>5.5424446</v>
+        <v>6.0463032</v>
       </c>
       <c r="N13">
-        <v>53.9325554</v>
+        <v>53.4286968</v>
       </c>
       <c r="O13">
-        <v>10.78651108</v>
+        <v>10.68573936</v>
       </c>
       <c r="P13">
-        <v>43.14604432</v>
+        <v>42.74295744</v>
       </c>
       <c r="Q13">
-        <v>78.04604431999999</v>
+        <v>77.64295744</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08697267141879042</v>
+        <v>0.08735538820089482</v>
       </c>
       <c r="T13">
-        <v>0.7810303625711055</v>
+        <v>0.7882903585050255</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.73082444522765</v>
+        <v>9.836589074792016</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08184554161678745</v>
+        <v>0.0819038056708514</v>
       </c>
       <c r="C14">
-        <v>837.3554544423621</v>
+        <v>826.1612273757644</v>
       </c>
       <c r="D14">
-        <v>909.1794544423622</v>
+        <v>907.7122273757644</v>
       </c>
       <c r="E14">
-        <v>-216.376</v>
+        <v>-206.649</v>
       </c>
       <c r="F14">
-        <v>116.724</v>
+        <v>126.451</v>
       </c>
       <c r="G14">
         <v>44.9</v>
@@ -2569,45 +2569,45 @@
         <v>59.475</v>
       </c>
       <c r="M14">
-        <v>6.0463032</v>
+        <v>6.7651285</v>
       </c>
       <c r="N14">
-        <v>53.4286968</v>
+        <v>52.7098715</v>
       </c>
       <c r="O14">
-        <v>10.68573936</v>
+        <v>10.5419743</v>
       </c>
       <c r="P14">
-        <v>42.74295744</v>
+        <v>42.1678972</v>
       </c>
       <c r="Q14">
-        <v>77.64295744</v>
+        <v>77.0678972</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08735538820089482</v>
+        <v>0.08774690306994413</v>
       </c>
       <c r="T14">
-        <v>0.7882903585050255</v>
+        <v>0.7957172508971964</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.836589074792016</v>
+        <v>8.791407288124681</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0819038056708514</v>
+        <v>0.08179886972491536</v>
       </c>
       <c r="C15">
-        <v>826.1612273757644</v>
+        <v>819.0801893724951</v>
       </c>
       <c r="D15">
-        <v>907.7122273757644</v>
+        <v>910.3581893724951</v>
       </c>
       <c r="E15">
-        <v>-206.649</v>
+        <v>-196.922</v>
       </c>
       <c r="F15">
-        <v>126.451</v>
+        <v>136.178</v>
       </c>
       <c r="G15">
         <v>44.9</v>
@@ -2651,28 +2651,28 @@
         <v>59.475</v>
       </c>
       <c r="M15">
-        <v>6.7651285</v>
+        <v>7.285523000000001</v>
       </c>
       <c r="N15">
-        <v>52.7098715</v>
+        <v>52.189477</v>
       </c>
       <c r="O15">
-        <v>10.5419743</v>
+        <v>10.4378954</v>
       </c>
       <c r="P15">
-        <v>42.1678972</v>
+        <v>41.75158159999999</v>
       </c>
       <c r="Q15">
-        <v>77.0678972</v>
+        <v>76.65158159999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08774690306994413</v>
+        <v>0.0881475229359481</v>
       </c>
       <c r="T15">
-        <v>0.7957172508971964</v>
+        <v>0.8033168617170923</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.791407288124681</v>
+        <v>8.163449624687203</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08179886972491536</v>
+        <v>0.08169393377897931</v>
       </c>
       <c r="C16">
-        <v>819.0801893724951</v>
+        <v>812.0146223135225</v>
       </c>
       <c r="D16">
-        <v>910.3581893724951</v>
+        <v>913.0196223135225</v>
       </c>
       <c r="E16">
-        <v>-196.922</v>
+        <v>-187.195</v>
       </c>
       <c r="F16">
-        <v>136.178</v>
+        <v>145.905</v>
       </c>
       <c r="G16">
         <v>44.9</v>
@@ -2733,28 +2733,28 @@
         <v>59.475</v>
       </c>
       <c r="M16">
-        <v>7.285523000000001</v>
+        <v>7.805917500000001</v>
       </c>
       <c r="N16">
-        <v>52.189477</v>
+        <v>51.6690825</v>
       </c>
       <c r="O16">
-        <v>10.4378954</v>
+        <v>10.3338165</v>
       </c>
       <c r="P16">
-        <v>41.75158159999999</v>
+        <v>41.335266</v>
       </c>
       <c r="Q16">
-        <v>76.65158159999999</v>
+        <v>76.235266</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0881475229359481</v>
+        <v>0.08855756915174037</v>
       </c>
       <c r="T16">
-        <v>0.8033168617170923</v>
+        <v>0.8110952869092209</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.163449624687203</v>
+        <v>7.619219649708057</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08169393377897931</v>
+        <v>0.08169139783304327</v>
       </c>
       <c r="C17">
-        <v>812.0146223135225</v>
+        <v>802.3521327126855</v>
       </c>
       <c r="D17">
-        <v>913.0196223135225</v>
+        <v>913.0841327126856</v>
       </c>
       <c r="E17">
-        <v>-187.195</v>
+        <v>-177.468</v>
       </c>
       <c r="F17">
-        <v>145.905</v>
+        <v>155.632</v>
       </c>
       <c r="G17">
         <v>44.9</v>
@@ -2815,45 +2815,45 @@
         <v>59.475</v>
       </c>
       <c r="M17">
-        <v>7.8059175</v>
+        <v>8.450817600000001</v>
       </c>
       <c r="N17">
-        <v>51.6690825</v>
+        <v>51.0241824</v>
       </c>
       <c r="O17">
-        <v>10.3338165</v>
+        <v>10.20483648</v>
       </c>
       <c r="P17">
-        <v>41.335266</v>
+        <v>40.81934592</v>
       </c>
       <c r="Q17">
-        <v>76.235266</v>
+        <v>75.71934591999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08855756915174037</v>
+        <v>0.08897737837267057</v>
       </c>
       <c r="T17">
-        <v>0.8110952869092209</v>
+        <v>0.8190589127011622</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.619219649708058</v>
+        <v>7.037780581135723</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08169139783304327</v>
+        <v>0.08159286188710724</v>
       </c>
       <c r="C18">
-        <v>802.3521327126855</v>
+        <v>795.1388073392018</v>
       </c>
       <c r="D18">
-        <v>913.0841327126856</v>
+        <v>915.5978073392018</v>
       </c>
       <c r="E18">
-        <v>-177.468</v>
+        <v>-167.741</v>
       </c>
       <c r="F18">
-        <v>155.632</v>
+        <v>165.359</v>
       </c>
       <c r="G18">
         <v>44.9</v>
@@ -2897,28 +2897,28 @@
         <v>59.475</v>
       </c>
       <c r="M18">
-        <v>8.450817600000001</v>
+        <v>8.9789937</v>
       </c>
       <c r="N18">
-        <v>51.0241824</v>
+        <v>50.4960063</v>
       </c>
       <c r="O18">
-        <v>10.20483648</v>
+        <v>10.09920126</v>
       </c>
       <c r="P18">
-        <v>40.81934592</v>
+        <v>40.39680504</v>
       </c>
       <c r="Q18">
-        <v>75.71934591999999</v>
+        <v>75.29680504000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08897737837267057</v>
+        <v>0.08940730347844246</v>
       </c>
       <c r="T18">
-        <v>0.8190589127011622</v>
+        <v>0.8272144330904997</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.037780581135723</v>
+        <v>6.62379348812774</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08159286188710724</v>
+        <v>0.0814943259411712</v>
       </c>
       <c r="C19">
-        <v>795.1388073392018</v>
+        <v>787.9393602111015</v>
       </c>
       <c r="D19">
-        <v>915.5978073392018</v>
+        <v>918.1253602111016</v>
       </c>
       <c r="E19">
-        <v>-167.741</v>
+        <v>-158.014</v>
       </c>
       <c r="F19">
-        <v>165.359</v>
+        <v>175.086</v>
       </c>
       <c r="G19">
         <v>44.9</v>
@@ -2979,28 +2979,28 @@
         <v>59.475</v>
       </c>
       <c r="M19">
-        <v>8.9789937</v>
+        <v>9.507169800000002</v>
       </c>
       <c r="N19">
-        <v>50.4960063</v>
+        <v>49.9678302</v>
       </c>
       <c r="O19">
-        <v>10.09920126</v>
+        <v>9.993566040000001</v>
       </c>
       <c r="P19">
-        <v>40.39680504</v>
+        <v>39.97426416</v>
       </c>
       <c r="Q19">
-        <v>75.29680504000001</v>
+        <v>74.87426416</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08940730347844246</v>
+        <v>0.08984771456240391</v>
       </c>
       <c r="T19">
-        <v>0.8272144330904997</v>
+        <v>0.8355688686112845</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.62379348812774</v>
+        <v>6.255804961009531</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0814943259411712</v>
+        <v>0.08154778999523517</v>
       </c>
       <c r="C20">
-        <v>787.9393602111015</v>
+        <v>776.8392206715001</v>
       </c>
       <c r="D20">
-        <v>918.1253602111016</v>
+        <v>916.7522206715001</v>
       </c>
       <c r="E20">
-        <v>-158.014</v>
+        <v>-148.287</v>
       </c>
       <c r="F20">
-        <v>175.086</v>
+        <v>184.813</v>
       </c>
       <c r="G20">
         <v>44.9</v>
@@ -3061,45 +3061,45 @@
         <v>59.475</v>
       </c>
       <c r="M20">
-        <v>9.507169800000002</v>
+        <v>10.2201589</v>
       </c>
       <c r="N20">
-        <v>49.9678302</v>
+        <v>49.2548411</v>
       </c>
       <c r="O20">
-        <v>9.993566040000001</v>
+        <v>9.85096822</v>
       </c>
       <c r="P20">
-        <v>39.97426416</v>
+        <v>39.40387288</v>
       </c>
       <c r="Q20">
-        <v>74.87426416</v>
+        <v>74.30387288</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0898477145624039</v>
+        <v>0.09029899999411749</v>
       </c>
       <c r="T20">
-        <v>0.8355688686112844</v>
+        <v>0.8441295864906072</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.255804961009531</v>
+        <v>5.819381144846974</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08154778999523517</v>
+        <v>0.08145725404929911</v>
       </c>
       <c r="C21">
-        <v>776.8392206715001</v>
+        <v>769.4399105539774</v>
       </c>
       <c r="D21">
-        <v>916.7522206715001</v>
+        <v>919.0799105539774</v>
       </c>
       <c r="E21">
-        <v>-148.287</v>
+        <v>-138.56</v>
       </c>
       <c r="F21">
-        <v>184.813</v>
+        <v>194.54</v>
       </c>
       <c r="G21">
         <v>44.9</v>
@@ -3143,28 +3143,28 @@
         <v>59.475</v>
       </c>
       <c r="M21">
-        <v>10.2201589</v>
+        <v>10.758062</v>
       </c>
       <c r="N21">
-        <v>49.2548411</v>
+        <v>48.716938</v>
       </c>
       <c r="O21">
-        <v>9.85096822</v>
+        <v>9.7433876</v>
       </c>
       <c r="P21">
-        <v>39.40387288</v>
+        <v>38.9735504</v>
       </c>
       <c r="Q21">
-        <v>74.30387288</v>
+        <v>73.8735504</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09029899999411749</v>
+        <v>0.0907615675616239</v>
       </c>
       <c r="T21">
-        <v>0.8441295864906072</v>
+        <v>0.8529043223169127</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.819381144846974</v>
+        <v>5.528412087604626</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08145725404929911</v>
+        <v>0.08136671810336309</v>
       </c>
       <c r="C22">
-        <v>769.4399105539774</v>
+        <v>762.0524508188671</v>
       </c>
       <c r="D22">
-        <v>919.0799105539774</v>
+        <v>921.4194508188672</v>
       </c>
       <c r="E22">
-        <v>-138.56</v>
+        <v>-128.833</v>
       </c>
       <c r="F22">
-        <v>194.54</v>
+        <v>204.267</v>
       </c>
       <c r="G22">
         <v>44.9</v>
@@ -3225,28 +3225,28 @@
         <v>59.475</v>
       </c>
       <c r="M22">
-        <v>10.758062</v>
+        <v>11.2959651</v>
       </c>
       <c r="N22">
-        <v>48.716938</v>
+        <v>48.1790349</v>
       </c>
       <c r="O22">
-        <v>9.7433876</v>
+        <v>9.63580698</v>
       </c>
       <c r="P22">
-        <v>38.9735504</v>
+        <v>38.54322792</v>
       </c>
       <c r="Q22">
-        <v>73.8735504</v>
+        <v>73.44322792</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0907615675616239</v>
+        <v>0.09123584570045959</v>
       </c>
       <c r="T22">
-        <v>0.8529043223169127</v>
+        <v>0.861901203354011</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.528412087604626</v>
+        <v>5.265154369147262</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08136671810336309</v>
+        <v>0.08127618215742706</v>
       </c>
       <c r="C23">
-        <v>762.0524508188671</v>
+        <v>754.6769321934286</v>
       </c>
       <c r="D23">
-        <v>921.4194508188672</v>
+        <v>923.7709321934286</v>
       </c>
       <c r="E23">
-        <v>-128.833</v>
+        <v>-119.106</v>
       </c>
       <c r="F23">
-        <v>204.267</v>
+        <v>213.994</v>
       </c>
       <c r="G23">
         <v>44.9</v>
@@ -3307,28 +3307,28 @@
         <v>59.475</v>
       </c>
       <c r="M23">
-        <v>11.2959651</v>
+        <v>11.8338682</v>
       </c>
       <c r="N23">
-        <v>48.1790349</v>
+        <v>47.6411318</v>
       </c>
       <c r="O23">
-        <v>9.635806980000002</v>
+        <v>9.52822636</v>
       </c>
       <c r="P23">
-        <v>38.54322792000001</v>
+        <v>38.11290544</v>
       </c>
       <c r="Q23">
-        <v>73.44322792</v>
+        <v>73.01290544</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09123584570045959</v>
+        <v>0.09172228481721417</v>
       </c>
       <c r="T23">
-        <v>0.861901203354011</v>
+        <v>0.8711287736484709</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.265154369147264</v>
+        <v>5.02582917054966</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08127618215742706</v>
+        <v>0.08118564621149101</v>
       </c>
       <c r="C24">
-        <v>754.6769321934286</v>
+        <v>747.3134463334419</v>
       </c>
       <c r="D24">
-        <v>923.7709321934286</v>
+        <v>926.1344463334419</v>
       </c>
       <c r="E24">
-        <v>-119.106</v>
+        <v>-109.379</v>
       </c>
       <c r="F24">
-        <v>213.994</v>
+        <v>223.721</v>
       </c>
       <c r="G24">
         <v>44.9</v>
@@ -3389,28 +3389,28 @@
         <v>59.475</v>
       </c>
       <c r="M24">
-        <v>11.8338682</v>
+        <v>12.3717713</v>
       </c>
       <c r="N24">
-        <v>47.6411318</v>
+        <v>47.1032287</v>
       </c>
       <c r="O24">
-        <v>9.52822636</v>
+        <v>9.420645740000001</v>
       </c>
       <c r="P24">
-        <v>38.11290544</v>
+        <v>37.68258296</v>
       </c>
       <c r="Q24">
-        <v>73.01290544</v>
+        <v>72.58258296</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09172228481721417</v>
+        <v>0.09222135871622208</v>
       </c>
       <c r="T24">
-        <v>0.8711287736484709</v>
+        <v>0.8805960210934359</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.02582917054966</v>
+        <v>4.807314858786631</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08118564621149101</v>
+        <v>0.08109511026555496</v>
       </c>
       <c r="C25">
-        <v>747.3134463334419</v>
+        <v>739.9620858351145</v>
       </c>
       <c r="D25">
-        <v>926.1344463334419</v>
+        <v>928.5100858351146</v>
       </c>
       <c r="E25">
-        <v>-109.379</v>
+        <v>-99.65199999999999</v>
       </c>
       <c r="F25">
-        <v>223.721</v>
+        <v>233.448</v>
       </c>
       <c r="G25">
         <v>44.9</v>
@@ -3471,28 +3471,28 @@
         <v>59.475</v>
       </c>
       <c r="M25">
-        <v>12.3717713</v>
+        <v>12.9096744</v>
       </c>
       <c r="N25">
-        <v>47.1032287</v>
+        <v>46.5653256</v>
       </c>
       <c r="O25">
-        <v>9.420645740000001</v>
+        <v>9.313065120000001</v>
       </c>
       <c r="P25">
-        <v>37.68258296</v>
+        <v>37.25226048</v>
       </c>
       <c r="Q25">
-        <v>72.58258296</v>
+        <v>72.15226048</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09222135871622208</v>
+        <v>0.09273356613888811</v>
       </c>
       <c r="T25">
-        <v>0.8805960210934359</v>
+        <v>0.8903124066290582</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.807314858786631</v>
+        <v>4.607010073003854</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08109511026555496</v>
+        <v>0.08150457431961892</v>
       </c>
       <c r="C26">
-        <v>739.9620858351146</v>
+        <v>719.5868282594342</v>
       </c>
       <c r="D26">
-        <v>928.5100858351146</v>
+        <v>917.8618282594343</v>
       </c>
       <c r="E26">
-        <v>-99.65200000000002</v>
+        <v>-89.92500000000001</v>
       </c>
       <c r="F26">
-        <v>233.448</v>
+        <v>243.175</v>
       </c>
       <c r="G26">
         <v>44.9</v>
@@ -3553,45 +3553,45 @@
         <v>59.475</v>
       </c>
       <c r="M26">
-        <v>12.9096744</v>
+        <v>14.055515</v>
       </c>
       <c r="N26">
-        <v>46.5653256</v>
+        <v>45.419485</v>
       </c>
       <c r="O26">
-        <v>9.313065120000001</v>
+        <v>9.083897</v>
       </c>
       <c r="P26">
-        <v>37.25226048</v>
+        <v>36.335588</v>
       </c>
       <c r="Q26">
-        <v>72.15226048</v>
+        <v>71.23558800000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09273356613888811</v>
+        <v>0.09325943242615856</v>
       </c>
       <c r="T26">
-        <v>0.890312406629058</v>
+        <v>0.9002878957789634</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.607010073003855</v>
+        <v>4.231435134180426</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08150457431961892</v>
+        <v>0.08143403837368288</v>
       </c>
       <c r="C27">
-        <v>719.5868282594342</v>
+        <v>711.6766936850124</v>
       </c>
       <c r="D27">
-        <v>917.8618282594343</v>
+        <v>919.6786936850125</v>
       </c>
       <c r="E27">
-        <v>-89.92500000000001</v>
+        <v>-80.19800000000001</v>
       </c>
       <c r="F27">
-        <v>243.175</v>
+        <v>252.902</v>
       </c>
       <c r="G27">
         <v>44.9</v>
@@ -3635,28 +3635,28 @@
         <v>59.475</v>
       </c>
       <c r="M27">
-        <v>14.055515</v>
+        <v>14.6177356</v>
       </c>
       <c r="N27">
-        <v>45.419485</v>
+        <v>44.8572644</v>
       </c>
       <c r="O27">
-        <v>9.083897</v>
+        <v>8.971452879999999</v>
       </c>
       <c r="P27">
-        <v>36.335588</v>
+        <v>35.88581152</v>
       </c>
       <c r="Q27">
-        <v>71.23558800000001</v>
+        <v>70.78581152</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09325943242615856</v>
+        <v>0.09379951131578768</v>
       </c>
       <c r="T27">
-        <v>0.9002878957789634</v>
+        <v>0.9105329927437312</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.231435134180426</v>
+        <v>4.068687629019641</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08143403837368288</v>
+        <v>0.08211950242774685</v>
       </c>
       <c r="C28">
-        <v>711.6766936850124</v>
+        <v>684.5924436218073</v>
       </c>
       <c r="D28">
-        <v>919.6786936850125</v>
+        <v>902.3214436218074</v>
       </c>
       <c r="E28">
-        <v>-80.19800000000001</v>
+        <v>-70.471</v>
       </c>
       <c r="F28">
-        <v>252.902</v>
+        <v>262.629</v>
       </c>
       <c r="G28">
         <v>44.9</v>
@@ -3717,45 +3717,45 @@
         <v>59.475</v>
       </c>
       <c r="M28">
-        <v>14.6177356</v>
+        <v>16.0991577</v>
       </c>
       <c r="N28">
-        <v>44.8572644</v>
+        <v>43.3758423</v>
       </c>
       <c r="O28">
-        <v>8.971452879999999</v>
+        <v>8.67516846</v>
       </c>
       <c r="P28">
-        <v>35.88581152</v>
+        <v>34.70067384</v>
       </c>
       <c r="Q28">
-        <v>70.78581152</v>
+        <v>69.60067384</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09379951131578768</v>
+        <v>0.09435438688732445</v>
       </c>
       <c r="T28">
-        <v>0.9105329927437312</v>
+        <v>0.9210587772965748</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.068687629019641</v>
+        <v>3.694292652341681</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08211950242774685</v>
+        <v>0.0820769664818108</v>
       </c>
       <c r="C29">
-        <v>684.5924436218073</v>
+        <v>675.9234454302573</v>
       </c>
       <c r="D29">
-        <v>902.3214436218074</v>
+        <v>903.3794454302574</v>
       </c>
       <c r="E29">
-        <v>-70.471</v>
+        <v>-60.74399999999997</v>
       </c>
       <c r="F29">
-        <v>262.629</v>
+        <v>272.3560000000001</v>
       </c>
       <c r="G29">
         <v>44.9</v>
@@ -3799,28 +3799,28 @@
         <v>59.475</v>
       </c>
       <c r="M29">
-        <v>16.0991577</v>
+        <v>16.6954228</v>
       </c>
       <c r="N29">
-        <v>43.3758423</v>
+        <v>42.7795772</v>
       </c>
       <c r="O29">
-        <v>8.67516846</v>
+        <v>8.55591544</v>
       </c>
       <c r="P29">
-        <v>34.70067384</v>
+        <v>34.22366176</v>
       </c>
       <c r="Q29">
-        <v>69.60067384</v>
+        <v>69.12366176</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09435438688732445</v>
+        <v>0.09492467566918167</v>
       </c>
       <c r="T29">
-        <v>0.9210587772965748</v>
+        <v>0.931876944753664</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.694292652341681</v>
+        <v>3.562353629043764</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0820769664818108</v>
+        <v>0.08268403053587477</v>
       </c>
       <c r="C30">
-        <v>675.9234454302573</v>
+        <v>651.3279730715344</v>
       </c>
       <c r="D30">
-        <v>903.3794454302574</v>
+        <v>888.5109730715344</v>
       </c>
       <c r="E30">
-        <v>-60.74399999999997</v>
+        <v>-51.017</v>
       </c>
       <c r="F30">
-        <v>272.3560000000001</v>
+        <v>282.083</v>
       </c>
       <c r="G30">
         <v>44.9</v>
@@ -3881,45 +3881,45 @@
         <v>59.475</v>
       </c>
       <c r="M30">
-        <v>16.6954228</v>
+        <v>18.0815203</v>
       </c>
       <c r="N30">
-        <v>42.7795772</v>
+        <v>41.3934797</v>
       </c>
       <c r="O30">
-        <v>8.55591544</v>
+        <v>8.27869594</v>
       </c>
       <c r="P30">
-        <v>34.22366176</v>
+        <v>33.11478376</v>
       </c>
       <c r="Q30">
-        <v>69.12366176</v>
+        <v>68.01478376</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09492467566918167</v>
+        <v>0.09551102892376728</v>
       </c>
       <c r="T30">
-        <v>0.931876944753664</v>
+        <v>0.9429998493222205</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.562353629043764</v>
+        <v>3.289269874060313</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08268403053587477</v>
+        <v>0.08266389458993872</v>
       </c>
       <c r="C31">
-        <v>651.3279730715344</v>
+        <v>642.0862991369531</v>
       </c>
       <c r="D31">
-        <v>888.5109730715344</v>
+        <v>888.9962991369532</v>
       </c>
       <c r="E31">
-        <v>-51.01700000000005</v>
+        <v>-41.29000000000002</v>
       </c>
       <c r="F31">
-        <v>282.083</v>
+        <v>291.81</v>
       </c>
       <c r="G31">
         <v>44.9</v>
@@ -3963,28 +3963,28 @@
         <v>59.475</v>
       </c>
       <c r="M31">
-        <v>18.0815203</v>
+        <v>18.705021</v>
       </c>
       <c r="N31">
-        <v>41.3934797</v>
+        <v>40.769979</v>
       </c>
       <c r="O31">
-        <v>8.27869594</v>
+        <v>8.153995800000001</v>
       </c>
       <c r="P31">
-        <v>33.11478376</v>
+        <v>32.6159832</v>
       </c>
       <c r="Q31">
-        <v>68.01478376</v>
+        <v>67.51598319999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09551102892376728</v>
+        <v>0.09611413512848389</v>
       </c>
       <c r="T31">
-        <v>0.9429998493222205</v>
+        <v>0.9544405511641644</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.289269874060314</v>
+        <v>3.179627544924969</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08266389458993872</v>
+        <v>0.08264375864400268</v>
       </c>
       <c r="C32">
-        <v>642.0862991369531</v>
+        <v>632.8451556856762</v>
       </c>
       <c r="D32">
-        <v>888.9962991369532</v>
+        <v>889.4821556856763</v>
       </c>
       <c r="E32">
-        <v>-41.29000000000002</v>
+        <v>-31.56299999999999</v>
       </c>
       <c r="F32">
-        <v>291.81</v>
+        <v>301.537</v>
       </c>
       <c r="G32">
         <v>44.9</v>
@@ -4045,28 +4045,28 @@
         <v>59.475</v>
       </c>
       <c r="M32">
-        <v>18.705021</v>
+        <v>19.3285217</v>
       </c>
       <c r="N32">
-        <v>40.769979</v>
+        <v>40.1464783</v>
       </c>
       <c r="O32">
-        <v>8.153995800000001</v>
+        <v>8.029295660000001</v>
       </c>
       <c r="P32">
-        <v>32.6159832</v>
+        <v>32.11718264</v>
       </c>
       <c r="Q32">
-        <v>67.51598319999999</v>
+        <v>67.01718263999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09611413512848389</v>
+        <v>0.09673472267246766</v>
       </c>
       <c r="T32">
-        <v>0.9544405511641644</v>
+        <v>0.9662128675522514</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.179627544924969</v>
+        <v>3.077058914443519</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08264375864400268</v>
+        <v>0.08462042269806665</v>
       </c>
       <c r="C33">
-        <v>632.8451556856762</v>
+        <v>577.8273710502281</v>
       </c>
       <c r="D33">
-        <v>889.4821556856763</v>
+        <v>844.1913710502281</v>
       </c>
       <c r="E33">
-        <v>-31.56299999999999</v>
+        <v>-21.83600000000001</v>
       </c>
       <c r="F33">
-        <v>301.537</v>
+        <v>311.264</v>
       </c>
       <c r="G33">
         <v>44.9</v>
@@ -4127,45 +4127,45 @@
         <v>59.475</v>
       </c>
       <c r="M33">
-        <v>19.3285217</v>
+        <v>22.3798816</v>
       </c>
       <c r="N33">
-        <v>40.1464783</v>
+        <v>37.0951184</v>
       </c>
       <c r="O33">
-        <v>8.029295660000001</v>
+        <v>7.419023680000001</v>
       </c>
       <c r="P33">
-        <v>32.11718264</v>
+        <v>29.67609472</v>
       </c>
       <c r="Q33">
-        <v>67.01718263999999</v>
+        <v>64.57609472</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09673472267246766</v>
+        <v>0.09737356279127449</v>
       </c>
       <c r="T33">
-        <v>0.9662128675522514</v>
+        <v>0.9783314285399882</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.077058914443519</v>
+        <v>2.657520761861403</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08462042269806665</v>
+        <v>0.08466268675213061</v>
       </c>
       <c r="C34">
-        <v>577.8273710502281</v>
+        <v>567.1822937702407</v>
       </c>
       <c r="D34">
-        <v>844.1913710502281</v>
+        <v>843.2732937702407</v>
       </c>
       <c r="E34">
-        <v>-21.83600000000001</v>
+        <v>-12.10899999999998</v>
       </c>
       <c r="F34">
-        <v>311.264</v>
+        <v>320.991</v>
       </c>
       <c r="G34">
         <v>44.9</v>
@@ -4209,28 +4209,28 @@
         <v>59.475</v>
       </c>
       <c r="M34">
-        <v>22.3798816</v>
+        <v>23.0792529</v>
       </c>
       <c r="N34">
-        <v>37.0951184</v>
+        <v>36.39574709999999</v>
       </c>
       <c r="O34">
-        <v>7.419023680000001</v>
+        <v>7.27914942</v>
       </c>
       <c r="P34">
-        <v>29.67609472</v>
+        <v>29.11659767999999</v>
       </c>
       <c r="Q34">
-        <v>64.57609472</v>
+        <v>64.01659767999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09737356279127449</v>
+        <v>0.09803147276437404</v>
       </c>
       <c r="T34">
-        <v>0.9783314285399882</v>
+        <v>0.9908117376169112</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.657520761861403</v>
+        <v>2.576989829683785</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08466268675213061</v>
+        <v>0.08470495080619454</v>
       </c>
       <c r="C35">
-        <v>567.1822937702407</v>
+        <v>556.5392111807491</v>
       </c>
       <c r="D35">
-        <v>843.2732937702407</v>
+        <v>842.3572111807492</v>
       </c>
       <c r="E35">
-        <v>-12.10899999999998</v>
+        <v>-2.382000000000005</v>
       </c>
       <c r="F35">
-        <v>320.991</v>
+        <v>330.718</v>
       </c>
       <c r="G35">
         <v>44.9</v>
@@ -4291,28 +4291,28 @@
         <v>59.475</v>
       </c>
       <c r="M35">
-        <v>23.0792529</v>
+        <v>23.7786242</v>
       </c>
       <c r="N35">
-        <v>36.39574709999999</v>
+        <v>35.6963758</v>
       </c>
       <c r="O35">
-        <v>7.27914942</v>
+        <v>7.13927516</v>
       </c>
       <c r="P35">
-        <v>29.11659767999999</v>
+        <v>28.55710064</v>
       </c>
       <c r="Q35">
-        <v>64.01659767999999</v>
+        <v>63.45710063999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09803147276437404</v>
+        <v>0.09870931940332509</v>
       </c>
       <c r="T35">
-        <v>0.9908117376169112</v>
+        <v>1.003670237877983</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.576989829683785</v>
+        <v>2.501196011163673</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08470495080619454</v>
+        <v>0.08583921486025853</v>
       </c>
       <c r="C36">
-        <v>556.5392111807491</v>
+        <v>522.9492181460815</v>
       </c>
       <c r="D36">
-        <v>842.3572111807492</v>
+        <v>818.4942181460816</v>
       </c>
       <c r="E36">
-        <v>-2.382000000000005</v>
+        <v>7.345000000000027</v>
       </c>
       <c r="F36">
-        <v>330.718</v>
+        <v>340.4450000000001</v>
       </c>
       <c r="G36">
         <v>44.9</v>
@@ -4373,45 +4373,45 @@
         <v>59.475</v>
       </c>
       <c r="M36">
-        <v>23.7786242</v>
+        <v>25.80573100000001</v>
       </c>
       <c r="N36">
-        <v>35.6963758</v>
+        <v>33.669269</v>
       </c>
       <c r="O36">
-        <v>7.13927516</v>
+        <v>6.7338538</v>
       </c>
       <c r="P36">
-        <v>28.55710064</v>
+        <v>26.9354152</v>
       </c>
       <c r="Q36">
-        <v>63.45710063999999</v>
+        <v>61.8354152</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09870931940332509</v>
+        <v>0.0994080228619362</v>
       </c>
       <c r="T36">
-        <v>1.003670237877983</v>
+        <v>1.016924384300935</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.501196011163673</v>
+        <v>2.304720606442034</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08583921486025853</v>
+        <v>0.08591267891432249</v>
       </c>
       <c r="C37">
-        <v>522.9492181460815</v>
+        <v>511.7231932711448</v>
       </c>
       <c r="D37">
-        <v>818.4942181460816</v>
+        <v>816.9951932711449</v>
       </c>
       <c r="E37">
-        <v>7.345000000000027</v>
+        <v>17.07200000000006</v>
       </c>
       <c r="F37">
-        <v>340.4450000000001</v>
+        <v>350.1720000000001</v>
       </c>
       <c r="G37">
         <v>44.9</v>
@@ -4455,28 +4455,28 @@
         <v>59.475</v>
       </c>
       <c r="M37">
-        <v>25.80573100000001</v>
+        <v>26.54303760000001</v>
       </c>
       <c r="N37">
-        <v>33.669269</v>
+        <v>32.93196239999999</v>
       </c>
       <c r="O37">
-        <v>6.7338538</v>
+        <v>6.586392479999998</v>
       </c>
       <c r="P37">
-        <v>26.9354152</v>
+        <v>26.34556991999999</v>
       </c>
       <c r="Q37">
-        <v>61.8354152</v>
+        <v>61.24556991999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0994080228619362</v>
+        <v>0.1001285608036289</v>
       </c>
       <c r="T37">
-        <v>1.016924384300935</v>
+        <v>1.030592722799603</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.304720606442034</v>
+        <v>2.240700589596421</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08591267891432249</v>
+        <v>0.08598614296838646</v>
       </c>
       <c r="C38">
-        <v>511.7231932711449</v>
+        <v>500.5026491135059</v>
       </c>
       <c r="D38">
-        <v>816.9951932711449</v>
+        <v>815.5016491135059</v>
       </c>
       <c r="E38">
-        <v>17.072</v>
+        <v>26.79899999999998</v>
       </c>
       <c r="F38">
-        <v>350.172</v>
+        <v>359.899</v>
       </c>
       <c r="G38">
         <v>44.9</v>
@@ -4537,28 +4537,28 @@
         <v>59.475</v>
       </c>
       <c r="M38">
-        <v>26.54303760000001</v>
+        <v>27.2803442</v>
       </c>
       <c r="N38">
-        <v>32.9319624</v>
+        <v>32.1946558</v>
       </c>
       <c r="O38">
-        <v>6.58639248</v>
+        <v>6.43893116</v>
       </c>
       <c r="P38">
-        <v>26.34556992</v>
+        <v>25.75572464</v>
       </c>
       <c r="Q38">
-        <v>61.24556991999999</v>
+        <v>60.65572464</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1001285608036289</v>
+        <v>0.1008719729656928</v>
       </c>
       <c r="T38">
-        <v>1.030592722799603</v>
+        <v>1.044694976806166</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.240700589596422</v>
+        <v>2.180141114201924</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08598614296838646</v>
+        <v>0.08605960702245041</v>
       </c>
       <c r="C39">
-        <v>500.5026491135059</v>
+        <v>489.2875556702114</v>
       </c>
       <c r="D39">
-        <v>815.5016491135059</v>
+        <v>814.0135556702114</v>
       </c>
       <c r="E39">
-        <v>26.79899999999998</v>
+        <v>36.52600000000001</v>
       </c>
       <c r="F39">
-        <v>359.899</v>
+        <v>369.626</v>
       </c>
       <c r="G39">
         <v>44.9</v>
@@ -4619,28 +4619,28 @@
         <v>59.475</v>
       </c>
       <c r="M39">
-        <v>27.2803442</v>
+        <v>28.01765080000001</v>
       </c>
       <c r="N39">
-        <v>32.1946558</v>
+        <v>31.4573492</v>
       </c>
       <c r="O39">
-        <v>6.43893116</v>
+        <v>6.29146984</v>
       </c>
       <c r="P39">
-        <v>25.75572464</v>
+        <v>25.16587936</v>
       </c>
       <c r="Q39">
-        <v>60.65572464</v>
+        <v>60.06587936</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1008719729656928</v>
+        <v>0.1016393661652426</v>
       </c>
       <c r="T39">
-        <v>1.044694976806166</v>
+        <v>1.059252142232295</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.180141114201924</v>
+        <v>2.122768979617663</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08605960702245041</v>
+        <v>0.08613307107651436</v>
       </c>
       <c r="C40">
-        <v>489.2875556702114</v>
+        <v>478.0778831569011</v>
       </c>
       <c r="D40">
-        <v>814.0135556702114</v>
+        <v>812.5308831569012</v>
       </c>
       <c r="E40">
-        <v>36.52600000000001</v>
+        <v>46.25299999999999</v>
       </c>
       <c r="F40">
-        <v>369.626</v>
+        <v>379.353</v>
       </c>
       <c r="G40">
         <v>44.9</v>
@@ -4701,28 +4701,28 @@
         <v>59.475</v>
       </c>
       <c r="M40">
-        <v>28.01765080000001</v>
+        <v>28.7549574</v>
       </c>
       <c r="N40">
-        <v>31.4573492</v>
+        <v>30.7200426</v>
       </c>
       <c r="O40">
-        <v>6.29146984</v>
+        <v>6.14400852</v>
       </c>
       <c r="P40">
-        <v>25.16587936</v>
+        <v>24.57603408</v>
       </c>
       <c r="Q40">
-        <v>60.06587936</v>
+        <v>59.47603408</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1016393661652426</v>
+        <v>0.1024319197975645</v>
       </c>
       <c r="T40">
-        <v>1.059252142232295</v>
+        <v>1.074286591770756</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.122768979617663</v>
+        <v>2.068339005781313</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08613307107651436</v>
+        <v>0.08620653513057833</v>
       </c>
       <c r="C41">
-        <v>478.0778831569011</v>
+        <v>466.8736020058203</v>
       </c>
       <c r="D41">
-        <v>812.5308831569012</v>
+        <v>811.0536020058204</v>
       </c>
       <c r="E41">
-        <v>46.25299999999999</v>
+        <v>55.98000000000002</v>
       </c>
       <c r="F41">
-        <v>379.353</v>
+        <v>389.08</v>
       </c>
       <c r="G41">
         <v>44.9</v>
@@ -4783,28 +4783,28 @@
         <v>59.475</v>
       </c>
       <c r="M41">
-        <v>28.7549574</v>
+        <v>29.49226400000001</v>
       </c>
       <c r="N41">
-        <v>30.7200426</v>
+        <v>29.982736</v>
       </c>
       <c r="O41">
-        <v>6.14400852</v>
+        <v>5.996547199999999</v>
       </c>
       <c r="P41">
-        <v>24.57603408</v>
+        <v>23.9861888</v>
       </c>
       <c r="Q41">
-        <v>59.47603408</v>
+        <v>58.8861888</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1024319197975645</v>
+        <v>0.1032508918842972</v>
       </c>
       <c r="T41">
-        <v>1.074286591770756</v>
+        <v>1.089822189627166</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.068339005781313</v>
+        <v>2.01663053063678</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08620653513057833</v>
+        <v>0.0909375991846423</v>
       </c>
       <c r="C42">
-        <v>466.8736020058203</v>
+        <v>372.1366189388787</v>
       </c>
       <c r="D42">
-        <v>811.0536020058204</v>
+        <v>726.0436189388788</v>
       </c>
       <c r="E42">
-        <v>55.98000000000002</v>
+        <v>65.70700000000005</v>
       </c>
       <c r="F42">
-        <v>389.08</v>
+        <v>398.8070000000001</v>
       </c>
       <c r="G42">
         <v>44.9</v>
@@ -4865,45 +4865,45 @@
         <v>59.475</v>
       </c>
       <c r="M42">
-        <v>29.49226400000001</v>
+        <v>35.89263</v>
       </c>
       <c r="N42">
-        <v>29.982736</v>
+        <v>23.58237</v>
       </c>
       <c r="O42">
-        <v>5.996547199999999</v>
+        <v>4.716474</v>
       </c>
       <c r="P42">
-        <v>23.9861888</v>
+        <v>18.865896</v>
       </c>
       <c r="Q42">
-        <v>58.8861888</v>
+        <v>53.765896</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1032508918842972</v>
+        <v>0.1040976257366819</v>
       </c>
       <c r="T42">
-        <v>1.089822189627166</v>
+        <v>1.105884417919387</v>
       </c>
       <c r="U42">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.01663053063678</v>
+        <v>1.6570254116235</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0909375991846423</v>
+        <v>0.09112466323870624</v>
       </c>
       <c r="C43">
-        <v>372.1366189388787</v>
+        <v>359.4130900497245</v>
       </c>
       <c r="D43">
-        <v>726.0436189388788</v>
+        <v>723.0470900497246</v>
       </c>
       <c r="E43">
-        <v>65.70700000000005</v>
+        <v>75.43400000000003</v>
       </c>
       <c r="F43">
-        <v>398.8070000000001</v>
+        <v>408.534</v>
       </c>
       <c r="G43">
         <v>44.9</v>
@@ -4947,28 +4947,28 @@
         <v>59.475</v>
       </c>
       <c r="M43">
-        <v>35.89263</v>
+        <v>36.76806000000001</v>
       </c>
       <c r="N43">
-        <v>23.58237</v>
+        <v>22.70694</v>
       </c>
       <c r="O43">
-        <v>4.716474</v>
+        <v>4.541388</v>
       </c>
       <c r="P43">
-        <v>18.865896</v>
+        <v>18.165552</v>
       </c>
       <c r="Q43">
-        <v>53.765896</v>
+        <v>53.065552</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1040976257366819</v>
+        <v>0.1049735573081142</v>
       </c>
       <c r="T43">
-        <v>1.105884417919387</v>
+        <v>1.122500516152719</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.6570254116235</v>
+        <v>1.617572425632464</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09112466323870624</v>
+        <v>0.09131172729277021</v>
       </c>
       <c r="C44">
-        <v>359.4130900497246</v>
+        <v>346.7141940574286</v>
       </c>
       <c r="D44">
-        <v>723.0470900497246</v>
+        <v>720.0751940574287</v>
       </c>
       <c r="E44">
-        <v>75.43399999999997</v>
+        <v>85.161</v>
       </c>
       <c r="F44">
-        <v>408.534</v>
+        <v>418.261</v>
       </c>
       <c r="G44">
         <v>44.9</v>
@@ -5029,28 +5029,28 @@
         <v>59.475</v>
       </c>
       <c r="M44">
-        <v>36.76806</v>
+        <v>37.64349</v>
       </c>
       <c r="N44">
-        <v>22.70694</v>
+        <v>21.83151</v>
       </c>
       <c r="O44">
-        <v>4.541388</v>
+        <v>4.366302</v>
       </c>
       <c r="P44">
-        <v>18.165552</v>
+        <v>17.465208</v>
       </c>
       <c r="Q44">
-        <v>53.065552</v>
+        <v>52.365208</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1049735573081142</v>
+        <v>0.1058802233206495</v>
       </c>
       <c r="T44">
-        <v>1.122500516152718</v>
+        <v>1.139699635376693</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.617572425632465</v>
+        <v>1.579954462245663</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09131172729277021</v>
+        <v>0.09149879134683417</v>
       </c>
       <c r="C45">
-        <v>346.7141940574286</v>
+        <v>334.0396284640859</v>
       </c>
       <c r="D45">
-        <v>720.0751940574287</v>
+        <v>717.1276284640859</v>
       </c>
       <c r="E45">
-        <v>85.161</v>
+        <v>94.88799999999998</v>
       </c>
       <c r="F45">
-        <v>418.261</v>
+        <v>427.988</v>
       </c>
       <c r="G45">
         <v>44.9</v>
@@ -5111,28 +5111,28 @@
         <v>59.475</v>
       </c>
       <c r="M45">
-        <v>37.64349</v>
+        <v>38.51892</v>
       </c>
       <c r="N45">
-        <v>21.83151</v>
+        <v>20.95608</v>
       </c>
       <c r="O45">
-        <v>4.366302</v>
+        <v>4.191216</v>
       </c>
       <c r="P45">
-        <v>17.465208</v>
+        <v>16.764864</v>
       </c>
       <c r="Q45">
-        <v>52.365208</v>
+        <v>51.66486399999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1058802233206495</v>
+        <v>0.1068192702622039</v>
       </c>
       <c r="T45">
-        <v>1.139699635376693</v>
+        <v>1.157513008858667</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.579954462245663</v>
+        <v>1.544046406285534</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09149879134683417</v>
+        <v>0.09168585540089813</v>
       </c>
       <c r="C46">
-        <v>334.0396284640859</v>
+        <v>321.3890957045954</v>
       </c>
       <c r="D46">
-        <v>717.1276284640859</v>
+        <v>714.2040957045955</v>
       </c>
       <c r="E46">
-        <v>94.88799999999998</v>
+        <v>104.615</v>
       </c>
       <c r="F46">
-        <v>427.988</v>
+        <v>437.715</v>
       </c>
       <c r="G46">
         <v>44.9</v>
@@ -5193,28 +5193,28 @@
         <v>59.475</v>
       </c>
       <c r="M46">
-        <v>38.51892</v>
+        <v>39.39435</v>
       </c>
       <c r="N46">
-        <v>20.95608</v>
+        <v>20.08065</v>
       </c>
       <c r="O46">
-        <v>4.191216</v>
+        <v>4.01613</v>
       </c>
       <c r="P46">
-        <v>16.764864</v>
+        <v>16.06452</v>
       </c>
       <c r="Q46">
-        <v>51.66486399999999</v>
+        <v>50.96451999999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1068192702622039</v>
+        <v>0.1077924643652693</v>
       </c>
       <c r="T46">
-        <v>1.157513008858667</v>
+        <v>1.175974141376349</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.544046406285534</v>
+        <v>1.509734263923634</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09168585540089813</v>
+        <v>0.1143779392655544</v>
       </c>
       <c r="C47">
-        <v>321.3890957045954</v>
+        <v>75.33567047545392</v>
       </c>
       <c r="D47">
-        <v>714.2040957045955</v>
+        <v>477.877670475454</v>
       </c>
       <c r="E47">
-        <v>104.615</v>
+        <v>114.342</v>
       </c>
       <c r="F47">
-        <v>437.715</v>
+        <v>447.4420000000001</v>
       </c>
       <c r="G47">
         <v>44.9</v>
@@ -5275,45 +5275,45 @@
         <v>59.475</v>
       </c>
       <c r="M47">
-        <v>39.39435</v>
+        <v>65.68448560000002</v>
       </c>
       <c r="N47">
-        <v>20.08065</v>
+        <v>-6.209485600000015</v>
       </c>
       <c r="O47">
-        <v>4.01613</v>
+        <v>-1.241897120000003</v>
       </c>
       <c r="P47">
-        <v>16.06452</v>
+        <v>-4.967588480000012</v>
       </c>
       <c r="Q47">
-        <v>50.96451999999999</v>
+        <v>29.93241151999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1077924643652693</v>
+        <v>0.1094051607469181</v>
       </c>
       <c r="T47">
-        <v>1.175974141376349</v>
+        <v>1.206566395808046</v>
       </c>
       <c r="U47">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2</v>
+        <v>0.181092991615055</v>
       </c>
       <c r="W47">
-        <v>0.07199999999999999</v>
+        <v>0.1202155488309099</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.509734263923634</v>
+        <v>0.9054649580752747</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1143779392655544</v>
+        <v>0.1153879392655544</v>
       </c>
       <c r="C48">
-        <v>75.33567047545392</v>
+        <v>58.67274950589677</v>
       </c>
       <c r="D48">
-        <v>477.877670475454</v>
+        <v>470.9417495058968</v>
       </c>
       <c r="E48">
-        <v>114.342</v>
+        <v>124.069</v>
       </c>
       <c r="F48">
-        <v>447.4420000000001</v>
+        <v>457.169</v>
       </c>
       <c r="G48">
         <v>44.9</v>
@@ -5357,37 +5357,37 @@
         <v>59.475</v>
       </c>
       <c r="M48">
-        <v>65.68448560000002</v>
+        <v>67.11240920000002</v>
       </c>
       <c r="N48">
-        <v>-6.209485600000015</v>
+        <v>-7.637409200000015</v>
       </c>
       <c r="O48">
-        <v>-1.241897120000003</v>
+        <v>-1.527481840000003</v>
       </c>
       <c r="P48">
-        <v>-4.967588480000012</v>
+        <v>-6.109927360000012</v>
       </c>
       <c r="Q48">
-        <v>29.93241151999999</v>
+        <v>28.79007263999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1094051607469181</v>
+        <v>0.1106052581195015</v>
       </c>
       <c r="T48">
-        <v>1.206566395808046</v>
+        <v>1.229331799502537</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.181092991615055</v>
+        <v>0.1772399492402665</v>
       </c>
       <c r="W48">
-        <v>0.1202155488309099</v>
+        <v>0.1207811754515289</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9054649580752747</v>
+        <v>0.8861997462013327</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1153879392655544</v>
+        <v>0.1163979392655544</v>
       </c>
       <c r="C49">
-        <v>58.67274950589677</v>
+        <v>42.20828419247187</v>
       </c>
       <c r="D49">
-        <v>470.9417495058968</v>
+        <v>464.204284192472</v>
       </c>
       <c r="E49">
-        <v>124.069</v>
+        <v>133.796</v>
       </c>
       <c r="F49">
-        <v>457.169</v>
+        <v>466.8960000000001</v>
       </c>
       <c r="G49">
         <v>44.9</v>
@@ -5439,37 +5439,37 @@
         <v>59.475</v>
       </c>
       <c r="M49">
-        <v>67.11240920000002</v>
+        <v>68.54033280000002</v>
       </c>
       <c r="N49">
-        <v>-7.637409200000015</v>
+        <v>-9.065332800000014</v>
       </c>
       <c r="O49">
-        <v>-1.527481840000003</v>
+        <v>-1.813066560000003</v>
       </c>
       <c r="P49">
-        <v>-6.109927360000012</v>
+        <v>-7.252266240000012</v>
       </c>
       <c r="Q49">
-        <v>28.79007263999999</v>
+        <v>27.64773375999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1106052581195015</v>
+        <v>0.111851513083338</v>
       </c>
       <c r="T49">
-        <v>1.229331799502537</v>
+        <v>1.252972795646817</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1772399492402665</v>
+        <v>0.173547450297761</v>
       </c>
       <c r="W49">
-        <v>0.1207811754515289</v>
+        <v>0.1213232342962887</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8861997462013327</v>
+        <v>0.867737251488805</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1163979392655544</v>
+        <v>0.1174079392655543</v>
       </c>
       <c r="C50">
-        <v>42.20828419247192</v>
+        <v>25.93387713337904</v>
       </c>
       <c r="D50">
-        <v>464.204284192472</v>
+        <v>457.6568771333791</v>
       </c>
       <c r="E50">
-        <v>133.796</v>
+        <v>143.523</v>
       </c>
       <c r="F50">
-        <v>466.896</v>
+        <v>476.623</v>
       </c>
       <c r="G50">
         <v>44.9</v>
@@ -5521,37 +5521,37 @@
         <v>59.475</v>
       </c>
       <c r="M50">
-        <v>68.5403328</v>
+        <v>69.9682564</v>
       </c>
       <c r="N50">
-        <v>-9.0653328</v>
+        <v>-10.4932564</v>
       </c>
       <c r="O50">
-        <v>-1.81306656</v>
+        <v>-2.09865128</v>
       </c>
       <c r="P50">
-        <v>-7.25226624</v>
+        <v>-8.39460512</v>
       </c>
       <c r="Q50">
-        <v>27.64773376</v>
+        <v>26.50539488</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.111851513083338</v>
+        <v>0.1131466407908545</v>
       </c>
       <c r="T50">
-        <v>1.252972795646817</v>
+        <v>1.277540889679107</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.173547450297761</v>
+        <v>0.1700056655978067</v>
       </c>
       <c r="W50">
-        <v>0.1213232342962887</v>
+        <v>0.121843168290242</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8677372514888051</v>
+        <v>0.8500283279890336</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1174079392655543</v>
+        <v>0.1184179392655544</v>
       </c>
       <c r="C51">
-        <v>25.93387713337904</v>
+        <v>9.841598104812874</v>
       </c>
       <c r="D51">
-        <v>457.6568771333791</v>
+        <v>451.2915981048129</v>
       </c>
       <c r="E51">
-        <v>143.523</v>
+        <v>153.25</v>
       </c>
       <c r="F51">
-        <v>476.623</v>
+        <v>486.35</v>
       </c>
       <c r="G51">
         <v>44.9</v>
@@ -5603,37 +5603,37 @@
         <v>59.475</v>
       </c>
       <c r="M51">
-        <v>69.9682564</v>
+        <v>71.39618000000002</v>
       </c>
       <c r="N51">
-        <v>-10.4932564</v>
+        <v>-11.92118000000001</v>
       </c>
       <c r="O51">
-        <v>-2.09865128</v>
+        <v>-2.384236000000003</v>
       </c>
       <c r="P51">
-        <v>-8.39460512</v>
+        <v>-9.536944000000011</v>
       </c>
       <c r="Q51">
-        <v>26.50539488</v>
+        <v>25.36305599999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1131466407908545</v>
+        <v>0.1144935736066716</v>
       </c>
       <c r="T51">
-        <v>1.277540889679107</v>
+        <v>1.303091707472689</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1700056655978067</v>
+        <v>0.1666055522858506</v>
       </c>
       <c r="W51">
-        <v>0.121843168290242</v>
+        <v>0.1223423049244371</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8500283279890336</v>
+        <v>0.8330277614292527</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1184179392655544</v>
+        <v>0.1194279392655543</v>
       </c>
       <c r="C52">
-        <v>9.841598104812874</v>
+        <v>-6.07604798188396</v>
       </c>
       <c r="D52">
-        <v>451.2915981048129</v>
+        <v>445.1009520181161</v>
       </c>
       <c r="E52">
-        <v>153.25</v>
+        <v>162.977</v>
       </c>
       <c r="F52">
-        <v>486.35</v>
+        <v>496.0770000000001</v>
       </c>
       <c r="G52">
         <v>44.9</v>
@@ -5685,37 +5685,37 @@
         <v>59.475</v>
       </c>
       <c r="M52">
-        <v>71.39618000000002</v>
+        <v>72.82410360000002</v>
       </c>
       <c r="N52">
-        <v>-11.92118000000001</v>
+        <v>-13.34910360000001</v>
       </c>
       <c r="O52">
-        <v>-2.384236000000003</v>
+        <v>-2.669820720000003</v>
       </c>
       <c r="P52">
-        <v>-9.536944000000011</v>
+        <v>-10.67928288000001</v>
       </c>
       <c r="Q52">
-        <v>25.36305599999999</v>
+        <v>24.22071711999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1144935736066716</v>
+        <v>0.1158954832721138</v>
       </c>
       <c r="T52">
-        <v>1.303091707472689</v>
+        <v>1.329685415788458</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1666055522858506</v>
+        <v>0.1633387767508339</v>
       </c>
       <c r="W52">
-        <v>0.1223423049244371</v>
+        <v>0.1228218675729776</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8330277614292527</v>
+        <v>0.8166938837541694</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1194279392655543</v>
+        <v>0.1204379392655544</v>
       </c>
       <c r="C53">
-        <v>-6.07604798188396</v>
+        <v>-21.82615052144945</v>
       </c>
       <c r="D53">
-        <v>445.1009520181161</v>
+        <v>439.0778494785506</v>
       </c>
       <c r="E53">
-        <v>162.977</v>
+        <v>172.704</v>
       </c>
       <c r="F53">
-        <v>496.0770000000001</v>
+        <v>505.804</v>
       </c>
       <c r="G53">
         <v>44.9</v>
@@ -5767,37 +5767,37 @@
         <v>59.475</v>
       </c>
       <c r="M53">
-        <v>72.82410360000002</v>
+        <v>74.25202720000001</v>
       </c>
       <c r="N53">
-        <v>-13.34910360000001</v>
+        <v>-14.77702720000001</v>
       </c>
       <c r="O53">
-        <v>-2.669820720000003</v>
+        <v>-2.955405440000003</v>
       </c>
       <c r="P53">
-        <v>-10.67928288000001</v>
+        <v>-11.82162176000001</v>
       </c>
       <c r="Q53">
-        <v>24.22071711999999</v>
+        <v>23.07837823999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1158954832721138</v>
+        <v>0.1173558058402829</v>
       </c>
       <c r="T53">
-        <v>1.329685415788458</v>
+        <v>1.357387195284051</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1633387767508339</v>
+        <v>0.1601976464287025</v>
       </c>
       <c r="W53">
-        <v>0.1228218675729776</v>
+        <v>0.1232829855042665</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8166938837541694</v>
+        <v>0.8009882321435123</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1204379392655544</v>
+        <v>0.1509073020787662</v>
       </c>
       <c r="C54">
-        <v>-21.82615052144945</v>
+        <v>-158.8366221206078</v>
       </c>
       <c r="D54">
-        <v>439.0778494785506</v>
+        <v>311.7943778793923</v>
       </c>
       <c r="E54">
-        <v>172.704</v>
+        <v>182.431</v>
       </c>
       <c r="F54">
-        <v>505.804</v>
+        <v>515.5310000000001</v>
       </c>
       <c r="G54">
         <v>44.9</v>
@@ -5849,45 +5849,45 @@
         <v>59.475</v>
       </c>
       <c r="M54">
-        <v>74.25202720000001</v>
+        <v>103.5186248</v>
       </c>
       <c r="N54">
-        <v>-14.77702720000001</v>
+        <v>-44.04362480000001</v>
       </c>
       <c r="O54">
-        <v>-2.955405440000003</v>
+        <v>-8.808724960000003</v>
       </c>
       <c r="P54">
-        <v>-11.82162176000001</v>
+        <v>-35.23489984000001</v>
       </c>
       <c r="Q54">
-        <v>23.07837823999999</v>
+        <v>-0.3348998400000127</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1173558058402829</v>
+        <v>0.1206641481203141</v>
       </c>
       <c r="T54">
-        <v>1.357387195284051</v>
+        <v>1.420145225828139</v>
       </c>
       <c r="U54">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1601976464287025</v>
+        <v>0.1149068587704036</v>
       </c>
       <c r="W54">
-        <v>0.1232829855042665</v>
+        <v>0.177726702758903</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8009882321435123</v>
+        <v>0.5745342938520179</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1509073020787662</v>
+        <v>0.1524573020787662</v>
       </c>
       <c r="C55">
-        <v>-158.8366221206078</v>
+        <v>-173.0947819783375</v>
       </c>
       <c r="D55">
-        <v>311.7943778793923</v>
+        <v>307.2632180216626</v>
       </c>
       <c r="E55">
-        <v>182.431</v>
+        <v>192.158</v>
       </c>
       <c r="F55">
-        <v>515.5310000000001</v>
+        <v>525.258</v>
       </c>
       <c r="G55">
         <v>44.9</v>
@@ -5931,37 +5931,37 @@
         <v>59.475</v>
       </c>
       <c r="M55">
-        <v>103.5186248</v>
+        <v>105.4718064</v>
       </c>
       <c r="N55">
-        <v>-44.04362480000001</v>
+        <v>-45.9968064</v>
       </c>
       <c r="O55">
-        <v>-8.808724960000003</v>
+        <v>-9.199361280000002</v>
       </c>
       <c r="P55">
-        <v>-35.23489984000001</v>
+        <v>-36.79744512000001</v>
       </c>
       <c r="Q55">
-        <v>-0.3348998400000127</v>
+        <v>-1.897445120000008</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1206641481203141</v>
+        <v>0.1222916296011906</v>
       </c>
       <c r="T55">
-        <v>1.420145225828139</v>
+        <v>1.451017948128751</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1149068587704036</v>
+        <v>0.1127789539783591</v>
       </c>
       <c r="W55">
-        <v>0.177726702758903</v>
+        <v>0.1781539860411455</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5745342938520179</v>
+        <v>0.5638947698917954</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1524573020787662</v>
+        <v>0.1540073020787662</v>
       </c>
       <c r="C56">
-        <v>-173.0947819783375</v>
+        <v>-187.2231299353071</v>
       </c>
       <c r="D56">
-        <v>307.2632180216626</v>
+        <v>302.8618700646929</v>
       </c>
       <c r="E56">
-        <v>192.158</v>
+        <v>201.885</v>
       </c>
       <c r="F56">
-        <v>525.258</v>
+        <v>534.985</v>
       </c>
       <c r="G56">
         <v>44.9</v>
@@ -6013,37 +6013,37 @@
         <v>59.475</v>
       </c>
       <c r="M56">
-        <v>105.4718064</v>
+        <v>107.424988</v>
       </c>
       <c r="N56">
-        <v>-45.9968064</v>
+        <v>-47.949988</v>
       </c>
       <c r="O56">
-        <v>-9.199361280000002</v>
+        <v>-9.5899976</v>
       </c>
       <c r="P56">
-        <v>-36.79744512000001</v>
+        <v>-38.3599904</v>
       </c>
       <c r="Q56">
-        <v>-1.897445120000008</v>
+        <v>-3.459990400000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1222916296011906</v>
+        <v>0.1239914435923281</v>
       </c>
       <c r="T56">
-        <v>1.451017948128751</v>
+        <v>1.483262791420501</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1127789539783591</v>
+        <v>0.1107284275423889</v>
       </c>
       <c r="W56">
-        <v>0.1781539860411455</v>
+        <v>0.1785657317494883</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5638947698917954</v>
+        <v>0.5536421377119447</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1540073020787662</v>
+        <v>0.1555573020787662</v>
       </c>
       <c r="C57">
-        <v>-187.2231299353071</v>
+        <v>-201.2271656286899</v>
       </c>
       <c r="D57">
-        <v>302.8618700646929</v>
+        <v>298.5848343713103</v>
       </c>
       <c r="E57">
-        <v>201.885</v>
+        <v>211.6120000000001</v>
       </c>
       <c r="F57">
-        <v>534.985</v>
+        <v>544.7120000000001</v>
       </c>
       <c r="G57">
         <v>44.9</v>
@@ -6095,37 +6095,37 @@
         <v>59.475</v>
       </c>
       <c r="M57">
-        <v>107.424988</v>
+        <v>109.3781696</v>
       </c>
       <c r="N57">
-        <v>-47.949988</v>
+        <v>-49.90316960000002</v>
       </c>
       <c r="O57">
-        <v>-9.5899976</v>
+        <v>-9.980633920000004</v>
       </c>
       <c r="P57">
-        <v>-38.3599904</v>
+        <v>-39.92253568000002</v>
       </c>
       <c r="Q57">
-        <v>-3.459990400000002</v>
+        <v>-5.022535680000018</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1239914435923281</v>
+        <v>0.1257685218557901</v>
       </c>
       <c r="T57">
-        <v>1.483262791420501</v>
+        <v>1.516973309407331</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1107284275423889</v>
+        <v>0.1087511341934177</v>
       </c>
       <c r="W57">
-        <v>0.1785657317494883</v>
+        <v>0.1789627722539617</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5536421377119447</v>
+        <v>0.5437556709670883</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1555573020787662</v>
+        <v>0.1571073020787662</v>
       </c>
       <c r="C58">
-        <v>-201.2271656286899</v>
+        <v>-215.1120823568128</v>
       </c>
       <c r="D58">
-        <v>298.5848343713103</v>
+        <v>294.4269176431873</v>
       </c>
       <c r="E58">
-        <v>211.6120000000001</v>
+        <v>221.3390000000001</v>
       </c>
       <c r="F58">
-        <v>544.7120000000001</v>
+        <v>554.4390000000001</v>
       </c>
       <c r="G58">
         <v>44.9</v>
@@ -6177,37 +6177,37 @@
         <v>59.475</v>
       </c>
       <c r="M58">
-        <v>109.3781696</v>
+        <v>111.3313512</v>
       </c>
       <c r="N58">
-        <v>-49.90316960000002</v>
+        <v>-51.85635120000001</v>
       </c>
       <c r="O58">
-        <v>-9.980633920000004</v>
+        <v>-10.37127024</v>
       </c>
       <c r="P58">
-        <v>-39.92253568000002</v>
+        <v>-41.48508096000001</v>
       </c>
       <c r="Q58">
-        <v>-5.022535680000018</v>
+        <v>-6.585080960000013</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1257685218557901</v>
+        <v>0.1276282549222038</v>
       </c>
       <c r="T58">
-        <v>1.516973309407331</v>
+        <v>1.552251758463315</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1087511341934177</v>
+        <v>0.1068432195584454</v>
       </c>
       <c r="W58">
-        <v>0.1789627722539617</v>
+        <v>0.1793458815126642</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5437556709670883</v>
+        <v>0.5342160977922272</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1571073020787662</v>
+        <v>0.1586573020787662</v>
       </c>
       <c r="C59">
-        <v>-215.1120823568128</v>
+        <v>-228.8827881156872</v>
       </c>
       <c r="D59">
-        <v>294.4269176431873</v>
+        <v>290.3832118843129</v>
       </c>
       <c r="E59">
-        <v>221.3390000000001</v>
+        <v>231.066</v>
       </c>
       <c r="F59">
-        <v>554.4390000000001</v>
+        <v>564.1660000000001</v>
       </c>
       <c r="G59">
         <v>44.9</v>
@@ -6259,37 +6259,37 @@
         <v>59.475</v>
       </c>
       <c r="M59">
-        <v>111.3313512</v>
+        <v>113.2845328</v>
       </c>
       <c r="N59">
-        <v>-51.85635120000001</v>
+        <v>-53.80953280000001</v>
       </c>
       <c r="O59">
-        <v>-10.37127024</v>
+        <v>-10.76190656</v>
       </c>
       <c r="P59">
-        <v>-41.48508096000001</v>
+        <v>-43.04762624000001</v>
       </c>
       <c r="Q59">
-        <v>-6.585080960000013</v>
+        <v>-8.147626240000008</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1276282549222038</v>
+        <v>0.1295765467060659</v>
       </c>
       <c r="T59">
-        <v>1.552251758463315</v>
+        <v>1.589210133664823</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1068432195584454</v>
+        <v>0.1050010950832999</v>
       </c>
       <c r="W59">
-        <v>0.1793458815126642</v>
+        <v>0.1797157801072734</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5342160977922272</v>
+        <v>0.5250054754164992</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1586573020787662</v>
+        <v>0.1602073020787662</v>
       </c>
       <c r="C60">
-        <v>-228.8827881156871</v>
+        <v>-242.5439249255109</v>
       </c>
       <c r="D60">
-        <v>290.3832118843129</v>
+        <v>286.4490750744892</v>
       </c>
       <c r="E60">
-        <v>231.0659999999999</v>
+        <v>240.793</v>
       </c>
       <c r="F60">
-        <v>564.1659999999999</v>
+        <v>573.893</v>
       </c>
       <c r="G60">
         <v>44.9</v>
@@ -6341,37 +6341,37 @@
         <v>59.475</v>
       </c>
       <c r="M60">
-        <v>113.2845328</v>
+        <v>115.2377144</v>
       </c>
       <c r="N60">
-        <v>-53.80953279999999</v>
+        <v>-55.76271440000001</v>
       </c>
       <c r="O60">
-        <v>-10.76190656</v>
+        <v>-11.15254288</v>
       </c>
       <c r="P60">
-        <v>-43.04762623999999</v>
+        <v>-44.61017152000001</v>
       </c>
       <c r="Q60">
-        <v>-8.147626239999994</v>
+        <v>-9.71017152000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1295765467060658</v>
+        <v>0.1316198771135308</v>
       </c>
       <c r="T60">
-        <v>1.589210133664822</v>
+        <v>1.627971356437135</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1050010950832999</v>
+        <v>0.1032214155056168</v>
       </c>
       <c r="W60">
-        <v>0.1797157801072734</v>
+        <v>0.1800731397664722</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5250054754164992</v>
+        <v>0.5161070775280839</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1602073020787662</v>
+        <v>0.1617573020787662</v>
       </c>
       <c r="C61">
-        <v>-242.5439249255109</v>
+        <v>-256.0998866071466</v>
       </c>
       <c r="D61">
-        <v>286.4490750744892</v>
+        <v>282.6201133928535</v>
       </c>
       <c r="E61">
-        <v>240.793</v>
+        <v>250.52</v>
       </c>
       <c r="F61">
-        <v>573.893</v>
+        <v>583.62</v>
       </c>
       <c r="G61">
         <v>44.9</v>
@@ -6423,37 +6423,37 @@
         <v>59.475</v>
       </c>
       <c r="M61">
-        <v>115.2377144</v>
+        <v>117.190896</v>
       </c>
       <c r="N61">
-        <v>-55.76271440000001</v>
+        <v>-57.71589600000001</v>
       </c>
       <c r="O61">
-        <v>-11.15254288</v>
+        <v>-11.5431792</v>
       </c>
       <c r="P61">
-        <v>-44.61017152000001</v>
+        <v>-46.1727168</v>
       </c>
       <c r="Q61">
-        <v>-9.71017152000001</v>
+        <v>-11.2727168</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1316198771135308</v>
+        <v>0.1337653740413691</v>
       </c>
       <c r="T61">
-        <v>1.627971356437135</v>
+        <v>1.668670640348064</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1032214155056168</v>
+        <v>0.1015010585805232</v>
       </c>
       <c r="W61">
-        <v>0.1800731397664722</v>
+        <v>0.180418587437031</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5161070775280839</v>
+        <v>0.5075052929026158</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1617573020787662</v>
+        <v>0.1849959951122757</v>
       </c>
       <c r="C62">
-        <v>-256.0998866071466</v>
+        <v>-313.0101554571922</v>
       </c>
       <c r="D62">
-        <v>282.6201133928535</v>
+        <v>235.4368445428077</v>
       </c>
       <c r="E62">
-        <v>250.52</v>
+        <v>260.247</v>
       </c>
       <c r="F62">
-        <v>583.62</v>
+        <v>593.347</v>
       </c>
       <c r="G62">
         <v>44.9</v>
@@ -6505,45 +6505,45 @@
         <v>59.475</v>
       </c>
       <c r="M62">
-        <v>117.190896</v>
+        <v>139.9112226</v>
       </c>
       <c r="N62">
-        <v>-57.71589600000001</v>
+        <v>-80.43622260000001</v>
       </c>
       <c r="O62">
-        <v>-11.5431792</v>
+        <v>-16.08724452</v>
       </c>
       <c r="P62">
-        <v>-46.1727168</v>
+        <v>-64.34897808000001</v>
       </c>
       <c r="Q62">
-        <v>-11.2727168</v>
+        <v>-29.44897808000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1337653740413691</v>
+        <v>0.1368893401283515</v>
       </c>
       <c r="T62">
-        <v>1.668670640348064</v>
+        <v>1.727931122641233</v>
       </c>
       <c r="U62">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1015010585805232</v>
+        <v>0.08501819781824993</v>
       </c>
       <c r="W62">
-        <v>0.180418587437031</v>
+        <v>0.2157527089544567</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5075052929026158</v>
+        <v>0.4250909890912495</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1849959951122757</v>
+        <v>0.1868959951122757</v>
       </c>
       <c r="C63">
-        <v>-313.0101554571922</v>
+        <v>-325.9075502247786</v>
       </c>
       <c r="D63">
-        <v>235.4368445428077</v>
+        <v>232.2664497752215</v>
       </c>
       <c r="E63">
-        <v>260.247</v>
+        <v>269.974</v>
       </c>
       <c r="F63">
-        <v>593.347</v>
+        <v>603.0740000000001</v>
       </c>
       <c r="G63">
         <v>44.9</v>
@@ -6587,37 +6587,37 @@
         <v>59.475</v>
       </c>
       <c r="M63">
-        <v>139.9112226</v>
+        <v>142.2048492</v>
       </c>
       <c r="N63">
-        <v>-80.43622260000001</v>
+        <v>-82.72984920000002</v>
       </c>
       <c r="O63">
-        <v>-16.08724452</v>
+        <v>-16.54596984000001</v>
       </c>
       <c r="P63">
-        <v>-64.34897808000001</v>
+        <v>-66.18387936000002</v>
       </c>
       <c r="Q63">
-        <v>-29.44897808000001</v>
+        <v>-31.28387936000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1368893401283515</v>
+        <v>0.1392864280264661</v>
       </c>
       <c r="T63">
-        <v>1.727931122641233</v>
+        <v>1.773402994289687</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08501819781824993</v>
+        <v>0.08364693656311686</v>
       </c>
       <c r="W63">
-        <v>0.2157527089544567</v>
+        <v>0.2160760523584171</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4250909890912495</v>
+        <v>0.4182346828155843</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1868959951122757</v>
+        <v>0.1887959951122757</v>
       </c>
       <c r="C64">
-        <v>-325.9075502247786</v>
+        <v>-338.7206943802594</v>
       </c>
       <c r="D64">
-        <v>232.2664497752215</v>
+        <v>229.1803056197406</v>
       </c>
       <c r="E64">
-        <v>269.974</v>
+        <v>279.701</v>
       </c>
       <c r="F64">
-        <v>603.0740000000001</v>
+        <v>612.801</v>
       </c>
       <c r="G64">
         <v>44.9</v>
@@ -6669,37 +6669,37 @@
         <v>59.475</v>
       </c>
       <c r="M64">
-        <v>142.2048492</v>
+        <v>144.4984758</v>
       </c>
       <c r="N64">
-        <v>-82.72984920000002</v>
+        <v>-85.02347580000003</v>
       </c>
       <c r="O64">
-        <v>-16.54596984000001</v>
+        <v>-17.00469516000001</v>
       </c>
       <c r="P64">
-        <v>-66.18387936000002</v>
+        <v>-68.01878064000002</v>
       </c>
       <c r="Q64">
-        <v>-31.28387936000002</v>
+        <v>-33.11878064000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1392864280264661</v>
+        <v>0.1418130882433976</v>
       </c>
       <c r="T64">
-        <v>1.773402994289687</v>
+        <v>1.821332804946165</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08364693656311686</v>
+        <v>0.08231920741132136</v>
       </c>
       <c r="W64">
-        <v>0.2160760523584171</v>
+        <v>0.2163891308924104</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4182346828155843</v>
+        <v>0.4115960370566067</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1887959951122757</v>
+        <v>0.1906959951122757</v>
       </c>
       <c r="C65">
-        <v>-338.7206943802594</v>
+        <v>-351.452902221512</v>
       </c>
       <c r="D65">
-        <v>229.1803056197406</v>
+        <v>226.175097778488</v>
       </c>
       <c r="E65">
-        <v>279.701</v>
+        <v>289.428</v>
       </c>
       <c r="F65">
-        <v>612.801</v>
+        <v>622.528</v>
       </c>
       <c r="G65">
         <v>44.9</v>
@@ -6751,37 +6751,37 @@
         <v>59.475</v>
       </c>
       <c r="M65">
-        <v>144.4984758</v>
+        <v>146.7921024</v>
       </c>
       <c r="N65">
-        <v>-85.02347580000003</v>
+        <v>-87.31710240000001</v>
       </c>
       <c r="O65">
-        <v>-17.00469516000001</v>
+        <v>-17.46342048</v>
       </c>
       <c r="P65">
-        <v>-68.01878064000002</v>
+        <v>-69.85368192000001</v>
       </c>
       <c r="Q65">
-        <v>-33.11878064000002</v>
+        <v>-34.95368192000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1418130882433976</v>
+        <v>0.1444801184723808</v>
       </c>
       <c r="T65">
-        <v>1.821332804946165</v>
+        <v>1.871925382861336</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08231920741132136</v>
+        <v>0.08103296979551947</v>
       </c>
       <c r="W65">
-        <v>0.2163891308924104</v>
+        <v>0.2166924257222165</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4115960370566067</v>
+        <v>0.4051648489775973</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1906959951122757</v>
+        <v>0.1925959951122757</v>
       </c>
       <c r="C66">
-        <v>-351.452902221512</v>
+        <v>-364.1073164568286</v>
       </c>
       <c r="D66">
-        <v>226.175097778488</v>
+        <v>223.2476835431714</v>
       </c>
       <c r="E66">
-        <v>289.428</v>
+        <v>299.155</v>
       </c>
       <c r="F66">
-        <v>622.528</v>
+        <v>632.255</v>
       </c>
       <c r="G66">
         <v>44.9</v>
@@ -6833,37 +6833,37 @@
         <v>59.475</v>
       </c>
       <c r="M66">
-        <v>146.7921024</v>
+        <v>149.085729</v>
       </c>
       <c r="N66">
-        <v>-87.31710240000001</v>
+        <v>-89.61072900000002</v>
       </c>
       <c r="O66">
-        <v>-17.46342048</v>
+        <v>-17.92214580000001</v>
       </c>
       <c r="P66">
-        <v>-69.85368192000001</v>
+        <v>-71.68858320000001</v>
       </c>
       <c r="Q66">
-        <v>-34.95368192000002</v>
+        <v>-36.78858320000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1444801184723808</v>
+        <v>0.1472995504287346</v>
       </c>
       <c r="T66">
-        <v>1.871925382861336</v>
+        <v>1.925408965228803</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08103296979551947</v>
+        <v>0.07978630872174225</v>
       </c>
       <c r="W66">
-        <v>0.2166924257222165</v>
+        <v>0.2169863884034132</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4051648489775973</v>
+        <v>0.3989315436087111</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1925959951122757</v>
+        <v>0.1944959951122757</v>
       </c>
       <c r="C67">
-        <v>-364.1073164568286</v>
+        <v>-376.686919167559</v>
       </c>
       <c r="D67">
-        <v>223.2476835431714</v>
+        <v>220.3950808324411</v>
       </c>
       <c r="E67">
-        <v>299.155</v>
+        <v>308.8820000000001</v>
       </c>
       <c r="F67">
-        <v>632.255</v>
+        <v>641.9820000000001</v>
       </c>
       <c r="G67">
         <v>44.9</v>
@@ -6915,37 +6915,37 @@
         <v>59.475</v>
       </c>
       <c r="M67">
-        <v>149.085729</v>
+        <v>151.3793556</v>
       </c>
       <c r="N67">
-        <v>-89.61072900000002</v>
+        <v>-91.90435560000003</v>
       </c>
       <c r="O67">
-        <v>-17.92214580000001</v>
+        <v>-18.38087112000001</v>
       </c>
       <c r="P67">
-        <v>-71.68858320000001</v>
+        <v>-73.52348448000002</v>
       </c>
       <c r="Q67">
-        <v>-36.78858320000001</v>
+        <v>-38.62348448000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1472995504287346</v>
+        <v>0.1502848313236974</v>
       </c>
       <c r="T67">
-        <v>1.925408965228803</v>
+        <v>1.982038640676709</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07978630872174225</v>
+        <v>0.0785774252562613</v>
       </c>
       <c r="W67">
-        <v>0.2169863884034132</v>
+        <v>0.2172714431245736</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3989315436087111</v>
+        <v>0.3928871262813064</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1944959951122757</v>
+        <v>0.1963959951122757</v>
       </c>
       <c r="C68">
-        <v>-376.686919167559</v>
+        <v>-389.19454194089</v>
       </c>
       <c r="D68">
-        <v>220.3950808324411</v>
+        <v>217.6144580591101</v>
       </c>
       <c r="E68">
-        <v>308.8820000000001</v>
+        <v>318.609</v>
       </c>
       <c r="F68">
-        <v>641.9820000000001</v>
+        <v>651.7090000000001</v>
       </c>
       <c r="G68">
         <v>44.9</v>
@@ -6997,37 +6997,37 @@
         <v>59.475</v>
       </c>
       <c r="M68">
-        <v>151.3793556</v>
+        <v>153.6729822</v>
       </c>
       <c r="N68">
-        <v>-91.90435560000003</v>
+        <v>-94.19798220000001</v>
       </c>
       <c r="O68">
-        <v>-18.38087112000001</v>
+        <v>-18.83959644</v>
       </c>
       <c r="P68">
-        <v>-73.52348448000002</v>
+        <v>-75.35838576</v>
       </c>
       <c r="Q68">
-        <v>-38.62348448000002</v>
+        <v>-40.45838576000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1502848313236974</v>
+        <v>0.1534510383335064</v>
       </c>
       <c r="T68">
-        <v>1.982038640676709</v>
+        <v>2.042100417666913</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0785774252562613</v>
+        <v>0.0774046278643768</v>
       </c>
       <c r="W68">
-        <v>0.2172714431245736</v>
+        <v>0.21754798874958</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3928871262813064</v>
+        <v>0.3870231393218839</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1963959951122757</v>
+        <v>0.1982959951122757</v>
       </c>
       <c r="C69">
-        <v>-389.19454194089</v>
+        <v>-401.6328752451377</v>
       </c>
       <c r="D69">
-        <v>217.6144580591101</v>
+        <v>214.9031247548624</v>
       </c>
       <c r="E69">
-        <v>318.609</v>
+        <v>328.336</v>
       </c>
       <c r="F69">
-        <v>651.7090000000001</v>
+        <v>661.436</v>
       </c>
       <c r="G69">
         <v>44.9</v>
@@ -7079,37 +7079,37 @@
         <v>59.475</v>
       </c>
       <c r="M69">
-        <v>153.6729822</v>
+        <v>155.9666088</v>
       </c>
       <c r="N69">
-        <v>-94.19798220000001</v>
+        <v>-96.49160880000002</v>
       </c>
       <c r="O69">
-        <v>-18.83959644</v>
+        <v>-19.29832176000001</v>
       </c>
       <c r="P69">
-        <v>-75.35838576</v>
+        <v>-77.19328704000002</v>
       </c>
       <c r="Q69">
-        <v>-40.45838576000001</v>
+        <v>-42.29328704000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1534510383335064</v>
+        <v>0.1568151332814285</v>
       </c>
       <c r="T69">
-        <v>2.042100417666913</v>
+        <v>2.105916055719003</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0774046278643768</v>
+        <v>0.07626632451343007</v>
       </c>
       <c r="W69">
-        <v>0.21754798874958</v>
+        <v>0.2178164006797332</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3870231393218839</v>
+        <v>0.3813316225671504</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1982959951122757</v>
+        <v>0.2001959951122757</v>
       </c>
       <c r="C70">
-        <v>-401.6328752451377</v>
+        <v>-414.0044771128048</v>
       </c>
       <c r="D70">
-        <v>214.9031247548624</v>
+        <v>212.2585228871954</v>
       </c>
       <c r="E70">
-        <v>328.336</v>
+        <v>338.0630000000001</v>
       </c>
       <c r="F70">
-        <v>661.436</v>
+        <v>671.1630000000001</v>
       </c>
       <c r="G70">
         <v>44.9</v>
@@ -7161,37 +7161,37 @@
         <v>59.475</v>
       </c>
       <c r="M70">
-        <v>155.9666088</v>
+        <v>158.2602354</v>
       </c>
       <c r="N70">
-        <v>-96.49160880000002</v>
+        <v>-98.78523540000003</v>
       </c>
       <c r="O70">
-        <v>-19.29832176000001</v>
+        <v>-19.75704708000001</v>
       </c>
       <c r="P70">
-        <v>-77.19328704000002</v>
+        <v>-79.02818832000003</v>
       </c>
       <c r="Q70">
-        <v>-42.29328704000002</v>
+        <v>-44.12818832000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1568151332814285</v>
+        <v>0.1603962666130875</v>
       </c>
       <c r="T70">
-        <v>2.105916055719003</v>
+        <v>2.173848831709939</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07626632451343007</v>
+        <v>0.07516101546251081</v>
       </c>
       <c r="W70">
-        <v>0.2178164006797332</v>
+        <v>0.21807703255394</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3813316225671504</v>
+        <v>0.375805077312554</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2001959951122757</v>
+        <v>0.2020959951122757</v>
       </c>
       <c r="C71">
-        <v>-414.0044771128048</v>
+        <v>-426.3117811903082</v>
       </c>
       <c r="D71">
-        <v>212.2585228871954</v>
+        <v>209.6782188096919</v>
       </c>
       <c r="E71">
-        <v>338.0630000000001</v>
+        <v>347.7900000000001</v>
       </c>
       <c r="F71">
-        <v>671.1630000000001</v>
+        <v>680.8900000000001</v>
       </c>
       <c r="G71">
         <v>44.9</v>
@@ -7243,37 +7243,37 @@
         <v>59.475</v>
       </c>
       <c r="M71">
-        <v>158.2602354</v>
+        <v>160.553862</v>
       </c>
       <c r="N71">
-        <v>-98.78523540000003</v>
+        <v>-101.078862</v>
       </c>
       <c r="O71">
-        <v>-19.75704708000001</v>
+        <v>-20.21577240000001</v>
       </c>
       <c r="P71">
-        <v>-79.02818832000003</v>
+        <v>-80.86308960000004</v>
       </c>
       <c r="Q71">
-        <v>-44.12818832000003</v>
+        <v>-45.96308960000004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1603962666130875</v>
+        <v>0.164216142166857</v>
       </c>
       <c r="T71">
-        <v>2.173848831709939</v>
+        <v>2.246310459433604</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07516101546251081</v>
+        <v>0.07408728667018921</v>
       </c>
       <c r="W71">
-        <v>0.21807703255394</v>
+        <v>0.2183302178031694</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.375805077312554</v>
+        <v>0.370436433350946</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2020959951122757</v>
+        <v>0.2039959951122757</v>
       </c>
       <c r="C72">
-        <v>-426.3117811903082</v>
+        <v>-438.557104207624</v>
       </c>
       <c r="D72">
-        <v>209.6782188096919</v>
+        <v>207.1598957923761</v>
       </c>
       <c r="E72">
-        <v>347.7900000000001</v>
+        <v>357.5170000000001</v>
       </c>
       <c r="F72">
-        <v>680.8900000000001</v>
+        <v>690.6170000000001</v>
       </c>
       <c r="G72">
         <v>44.9</v>
@@ -7325,37 +7325,37 @@
         <v>59.475</v>
       </c>
       <c r="M72">
-        <v>160.553862</v>
+        <v>162.8474886</v>
       </c>
       <c r="N72">
-        <v>-101.078862</v>
+        <v>-103.3724886</v>
       </c>
       <c r="O72">
-        <v>-20.21577240000001</v>
+        <v>-20.67449772000001</v>
       </c>
       <c r="P72">
-        <v>-80.86308960000004</v>
+        <v>-82.69799088000002</v>
       </c>
       <c r="Q72">
-        <v>-45.96308960000004</v>
+        <v>-47.79799088000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.164216142166857</v>
+        <v>0.1682994574139901</v>
       </c>
       <c r="T72">
-        <v>2.246310459433604</v>
+        <v>2.323769440793384</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07408728667018921</v>
+        <v>0.07304380375934148</v>
       </c>
       <c r="W72">
-        <v>0.2183302178031694</v>
+        <v>0.2185762710735473</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.370436433350946</v>
+        <v>0.3652190187967074</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2039959951122757</v>
+        <v>0.2058959951122757</v>
       </c>
       <c r="C73">
-        <v>-438.5571042076239</v>
+        <v>-450.7426529160377</v>
       </c>
       <c r="D73">
-        <v>207.1598957923761</v>
+        <v>204.7013470839623</v>
       </c>
       <c r="E73">
-        <v>357.5169999999999</v>
+        <v>367.244</v>
       </c>
       <c r="F73">
-        <v>690.617</v>
+        <v>700.3440000000001</v>
       </c>
       <c r="G73">
         <v>44.9</v>
@@ -7407,37 +7407,37 @@
         <v>59.475</v>
       </c>
       <c r="M73">
-        <v>162.8474886</v>
+        <v>165.1411152</v>
       </c>
       <c r="N73">
-        <v>-103.3724886</v>
+        <v>-105.6661152</v>
       </c>
       <c r="O73">
-        <v>-20.67449772</v>
+        <v>-21.13322304000001</v>
       </c>
       <c r="P73">
-        <v>-82.69799087999999</v>
+        <v>-84.53289216000003</v>
       </c>
       <c r="Q73">
-        <v>-47.79799087999999</v>
+        <v>-49.63289216000003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.16829945741399</v>
+        <v>0.1726744380359182</v>
       </c>
       <c r="T73">
-        <v>2.323769440793383</v>
+        <v>2.406761206536003</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0730438037593415</v>
+        <v>0.07202930648490617</v>
       </c>
       <c r="W73">
-        <v>0.2185762710735473</v>
+        <v>0.2188154895308591</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3652190187967074</v>
+        <v>0.3601465324245309</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2058959951122757</v>
+        <v>0.2077959951122757</v>
       </c>
       <c r="C74">
-        <v>-450.7426529160377</v>
+        <v>-462.8705305376726</v>
       </c>
       <c r="D74">
-        <v>204.7013470839623</v>
+        <v>202.3004694623274</v>
       </c>
       <c r="E74">
-        <v>367.244</v>
+        <v>376.971</v>
       </c>
       <c r="F74">
-        <v>700.3440000000001</v>
+        <v>710.071</v>
       </c>
       <c r="G74">
         <v>44.9</v>
@@ -7489,37 +7489,37 @@
         <v>59.475</v>
       </c>
       <c r="M74">
-        <v>165.1411152</v>
+        <v>167.4347418</v>
       </c>
       <c r="N74">
-        <v>-105.6661152</v>
+        <v>-107.9597418</v>
       </c>
       <c r="O74">
-        <v>-21.13322304000001</v>
+        <v>-21.59194836</v>
       </c>
       <c r="P74">
-        <v>-84.53289216000003</v>
+        <v>-86.36779344000001</v>
       </c>
       <c r="Q74">
-        <v>-49.63289216000003</v>
+        <v>-51.46779344000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1726744380359182</v>
+        <v>0.1773734912965078</v>
       </c>
       <c r="T74">
-        <v>2.406761206536003</v>
+        <v>2.495900510481781</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07202930648490617</v>
+        <v>0.07104260365634583</v>
       </c>
       <c r="W74">
-        <v>0.2188154895308591</v>
+        <v>0.2190481540578336</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3601465324245309</v>
+        <v>0.3552130182817291</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2077959951122757</v>
+        <v>0.2096959951122757</v>
       </c>
       <c r="C75">
-        <v>-462.8705305376726</v>
+        <v>-474.9427427664102</v>
       </c>
       <c r="D75">
-        <v>202.3004694623274</v>
+        <v>199.9552572335898</v>
       </c>
       <c r="E75">
-        <v>376.971</v>
+        <v>386.698</v>
       </c>
       <c r="F75">
-        <v>710.071</v>
+        <v>719.798</v>
       </c>
       <c r="G75">
         <v>44.9</v>
@@ -7571,37 +7571,37 @@
         <v>59.475</v>
       </c>
       <c r="M75">
-        <v>167.4347418</v>
+        <v>169.7283684</v>
       </c>
       <c r="N75">
-        <v>-107.9597418</v>
+        <v>-110.2533684</v>
       </c>
       <c r="O75">
-        <v>-21.59194836</v>
+        <v>-22.05067368</v>
       </c>
       <c r="P75">
-        <v>-86.36779344000001</v>
+        <v>-88.20269472</v>
       </c>
       <c r="Q75">
-        <v>-51.46779344000002</v>
+        <v>-53.30269472</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1773734912965078</v>
+        <v>0.1824340101925273</v>
       </c>
       <c r="T75">
-        <v>2.495900510481781</v>
+        <v>2.59189668396185</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07104260365634583</v>
+        <v>0.07008256847180062</v>
       </c>
       <c r="W75">
-        <v>0.2190481540578336</v>
+        <v>0.2192745303543494</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3552130182817291</v>
+        <v>0.3504128423590031</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2096959951122757</v>
+        <v>0.2115959951122757</v>
       </c>
       <c r="C76">
-        <v>-474.9427427664102</v>
+        <v>-486.9612033561945</v>
       </c>
       <c r="D76">
-        <v>199.9552572335898</v>
+        <v>197.6637966438056</v>
       </c>
       <c r="E76">
-        <v>386.698</v>
+        <v>396.4250000000001</v>
       </c>
       <c r="F76">
-        <v>719.798</v>
+        <v>729.5250000000001</v>
       </c>
       <c r="G76">
         <v>44.9</v>
@@ -7653,37 +7653,37 @@
         <v>59.475</v>
       </c>
       <c r="M76">
-        <v>169.7283684</v>
+        <v>172.021995</v>
       </c>
       <c r="N76">
-        <v>-110.2533684</v>
+        <v>-112.546995</v>
       </c>
       <c r="O76">
-        <v>-22.05067368</v>
+        <v>-22.50939900000001</v>
       </c>
       <c r="P76">
-        <v>-88.20269472</v>
+        <v>-90.03759600000004</v>
       </c>
       <c r="Q76">
-        <v>-53.30269472</v>
+        <v>-55.13759600000004</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1824340101925273</v>
+        <v>0.1878993706002284</v>
       </c>
       <c r="T76">
-        <v>2.59189668396185</v>
+        <v>2.695572551320324</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07008256847180062</v>
+        <v>0.06914813422550993</v>
       </c>
       <c r="W76">
-        <v>0.2192745303543494</v>
+        <v>0.2194948699496248</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3504128423590031</v>
+        <v>0.3457406711275496</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2115959951122757</v>
+        <v>0.2134959951122757</v>
       </c>
       <c r="C77">
-        <v>-486.9612033561945</v>
+        <v>-498.9277393294403</v>
       </c>
       <c r="D77">
-        <v>197.6637966438056</v>
+        <v>195.4242606705597</v>
       </c>
       <c r="E77">
-        <v>396.4250000000001</v>
+        <v>406.152</v>
       </c>
       <c r="F77">
-        <v>729.5250000000001</v>
+        <v>739.2520000000001</v>
       </c>
       <c r="G77">
         <v>44.9</v>
@@ -7735,37 +7735,37 @@
         <v>59.475</v>
       </c>
       <c r="M77">
-        <v>172.021995</v>
+        <v>174.3156216</v>
       </c>
       <c r="N77">
-        <v>-112.546995</v>
+        <v>-114.8406216</v>
       </c>
       <c r="O77">
-        <v>-22.50939900000001</v>
+        <v>-22.96812432</v>
       </c>
       <c r="P77">
-        <v>-90.03759600000004</v>
+        <v>-91.87249728000002</v>
       </c>
       <c r="Q77">
-        <v>-55.13759600000004</v>
+        <v>-56.97249728000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1878993706002284</v>
+        <v>0.1938201777085713</v>
       </c>
       <c r="T77">
-        <v>2.695572551320324</v>
+        <v>2.807888074292004</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06914813422550993</v>
+        <v>0.06823829035412164</v>
       </c>
       <c r="W77">
-        <v>0.2194948699496248</v>
+        <v>0.2197094111344981</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3457406711275496</v>
+        <v>0.3411914517706082</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2134959951122757</v>
+        <v>0.2153959951122757</v>
       </c>
       <c r="C78">
-        <v>-498.9277393294403</v>
+        <v>-510.8440958353427</v>
       </c>
       <c r="D78">
-        <v>195.4242606705597</v>
+        <v>193.2349041646573</v>
       </c>
       <c r="E78">
-        <v>406.152</v>
+        <v>415.879</v>
       </c>
       <c r="F78">
-        <v>739.2520000000001</v>
+        <v>748.979</v>
       </c>
       <c r="G78">
         <v>44.9</v>
@@ -7817,37 +7817,37 @@
         <v>59.475</v>
       </c>
       <c r="M78">
-        <v>174.3156216</v>
+        <v>176.6092482</v>
       </c>
       <c r="N78">
-        <v>-114.8406216</v>
+        <v>-117.1342482</v>
       </c>
       <c r="O78">
-        <v>-22.96812432</v>
+        <v>-23.42684964000001</v>
       </c>
       <c r="P78">
-        <v>-91.87249728000002</v>
+        <v>-93.70739856000003</v>
       </c>
       <c r="Q78">
-        <v>-56.97249728000002</v>
+        <v>-58.80739856000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1938201777085713</v>
+        <v>0.200255837608944</v>
       </c>
       <c r="T78">
-        <v>2.807888074292004</v>
+        <v>2.929970164478613</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06823829035412164</v>
+        <v>0.06735207879108111</v>
       </c>
       <c r="W78">
-        <v>0.2197094111344981</v>
+        <v>0.2199183798210631</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3411914517706082</v>
+        <v>0.3367603939554055</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2153959951122757</v>
+        <v>0.2172959951122757</v>
       </c>
       <c r="C79">
-        <v>-510.8440958353427</v>
+        <v>-522.7119406852325</v>
       </c>
       <c r="D79">
-        <v>193.2349041646573</v>
+        <v>191.0940593147674</v>
       </c>
       <c r="E79">
-        <v>415.879</v>
+        <v>425.606</v>
       </c>
       <c r="F79">
-        <v>748.979</v>
+        <v>758.706</v>
       </c>
       <c r="G79">
         <v>44.9</v>
@@ -7899,37 +7899,37 @@
         <v>59.475</v>
       </c>
       <c r="M79">
-        <v>176.6092482</v>
+        <v>178.9028748</v>
       </c>
       <c r="N79">
-        <v>-117.1342482</v>
+        <v>-119.4278748</v>
       </c>
       <c r="O79">
-        <v>-23.42684964000001</v>
+        <v>-23.88557496</v>
       </c>
       <c r="P79">
-        <v>-93.70739856000003</v>
+        <v>-95.54229984000001</v>
       </c>
       <c r="Q79">
-        <v>-58.80739856000003</v>
+        <v>-60.64229984000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.200255837608944</v>
+        <v>0.2072765575002596</v>
       </c>
       <c r="T79">
-        <v>2.929970164478613</v>
+        <v>3.063150626500369</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06735207879108111</v>
+        <v>0.06648859060145187</v>
       </c>
       <c r="W79">
-        <v>0.2199183798210631</v>
+        <v>0.2201219903361777</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3367603939554055</v>
+        <v>0.3324429530072592</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2172959951122757</v>
+        <v>0.2191959951122757</v>
       </c>
       <c r="C80">
-        <v>-522.7119406852325</v>
+        <v>-534.5328685897554</v>
       </c>
       <c r="D80">
-        <v>191.0940593147674</v>
+        <v>189.0001314102448</v>
       </c>
       <c r="E80">
-        <v>425.606</v>
+        <v>435.3330000000001</v>
       </c>
       <c r="F80">
-        <v>758.706</v>
+        <v>768.4330000000001</v>
       </c>
       <c r="G80">
         <v>44.9</v>
@@ -7981,37 +7981,37 @@
         <v>59.475</v>
       </c>
       <c r="M80">
-        <v>178.9028748</v>
+        <v>181.1965014</v>
       </c>
       <c r="N80">
-        <v>-119.4278748</v>
+        <v>-121.7215014000001</v>
       </c>
       <c r="O80">
-        <v>-23.88557496</v>
+        <v>-24.34430028000001</v>
       </c>
       <c r="P80">
-        <v>-95.54229984000001</v>
+        <v>-97.37720112000004</v>
       </c>
       <c r="Q80">
-        <v>-60.64229984000001</v>
+        <v>-62.47720112000004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2072765575002596</v>
+        <v>0.2149659173812243</v>
       </c>
       <c r="T80">
-        <v>3.063150626500369</v>
+        <v>3.209014942048005</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06648859060145187</v>
+        <v>0.06564696287231955</v>
       </c>
       <c r="W80">
-        <v>0.2201219903361777</v>
+        <v>0.2203204461547071</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3324429530072592</v>
+        <v>0.3282348143615977</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2191959951122757</v>
+        <v>0.2210959951122757</v>
       </c>
       <c r="C81">
-        <v>-534.5328685897554</v>
+        <v>-546.3084051204926</v>
       </c>
       <c r="D81">
-        <v>189.0001314102448</v>
+        <v>186.9515948795075</v>
       </c>
       <c r="E81">
-        <v>435.3330000000001</v>
+        <v>445.0600000000001</v>
       </c>
       <c r="F81">
-        <v>768.4330000000001</v>
+        <v>778.1600000000001</v>
       </c>
       <c r="G81">
         <v>44.9</v>
@@ -8063,37 +8063,37 @@
         <v>59.475</v>
       </c>
       <c r="M81">
-        <v>181.1965014</v>
+        <v>183.490128</v>
       </c>
       <c r="N81">
-        <v>-121.7215014000001</v>
+        <v>-124.015128</v>
       </c>
       <c r="O81">
-        <v>-24.34430028000001</v>
+        <v>-24.80302560000001</v>
       </c>
       <c r="P81">
-        <v>-97.37720112000004</v>
+        <v>-99.21210240000002</v>
       </c>
       <c r="Q81">
-        <v>-62.47720112000004</v>
+        <v>-64.31210240000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2149659173812243</v>
+        <v>0.2234242132502856</v>
       </c>
       <c r="T81">
-        <v>3.209014942048005</v>
+        <v>3.369465689150406</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06564696287231955</v>
+        <v>0.06482637583641557</v>
       </c>
       <c r="W81">
-        <v>0.2203204461547071</v>
+        <v>0.2205139405777732</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3282348143615977</v>
+        <v>0.3241318791820778</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2210959951122757</v>
+        <v>0.2229959951122757</v>
       </c>
       <c r="C82">
-        <v>-546.3084051204926</v>
+        <v>-558.0400104167128</v>
       </c>
       <c r="D82">
-        <v>186.9515948795075</v>
+        <v>184.9469895832873</v>
       </c>
       <c r="E82">
-        <v>445.0600000000001</v>
+        <v>454.787</v>
       </c>
       <c r="F82">
-        <v>778.1600000000001</v>
+        <v>787.8870000000001</v>
       </c>
       <c r="G82">
         <v>44.9</v>
@@ -8145,37 +8145,37 @@
         <v>59.475</v>
       </c>
       <c r="M82">
-        <v>183.490128</v>
+        <v>185.7837546</v>
       </c>
       <c r="N82">
-        <v>-124.015128</v>
+        <v>-126.3087546</v>
       </c>
       <c r="O82">
-        <v>-24.80302560000001</v>
+        <v>-25.26175092</v>
       </c>
       <c r="P82">
-        <v>-99.21210240000002</v>
+        <v>-101.04700368</v>
       </c>
       <c r="Q82">
-        <v>-64.31210240000001</v>
+        <v>-66.14700368000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2234242132502856</v>
+        <v>0.2327728560529322</v>
       </c>
       <c r="T82">
-        <v>3.369465689150406</v>
+        <v>3.546805988579374</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06482637583641557</v>
+        <v>0.0640260502088055</v>
       </c>
       <c r="W82">
-        <v>0.2205139405777732</v>
+        <v>0.2207026573607637</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3241318791820778</v>
+        <v>0.3201302510440275</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2229959951122757</v>
+        <v>0.2248959951122757</v>
       </c>
       <c r="C83">
-        <v>-558.0400104167128</v>
+        <v>-569.7290826561727</v>
       </c>
       <c r="D83">
-        <v>184.9469895832873</v>
+        <v>182.9849173438274</v>
       </c>
       <c r="E83">
-        <v>454.787</v>
+        <v>464.5140000000001</v>
       </c>
       <c r="F83">
-        <v>787.8870000000001</v>
+        <v>797.6140000000001</v>
       </c>
       <c r="G83">
         <v>44.9</v>
@@ -8227,37 +8227,37 @@
         <v>59.475</v>
       </c>
       <c r="M83">
-        <v>185.7837546</v>
+        <v>188.0773812</v>
       </c>
       <c r="N83">
-        <v>-126.3087546</v>
+        <v>-128.6023812000001</v>
       </c>
       <c r="O83">
-        <v>-25.26175092</v>
+        <v>-25.72047624000001</v>
       </c>
       <c r="P83">
-        <v>-101.04700368</v>
+        <v>-102.88190496</v>
       </c>
       <c r="Q83">
-        <v>-66.14700368000001</v>
+        <v>-67.98190496000004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2327728560529322</v>
+        <v>0.2431602369447617</v>
       </c>
       <c r="T83">
-        <v>3.546805988579374</v>
+        <v>3.743850765722673</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0640260502088055</v>
+        <v>0.0632452447184542</v>
       </c>
       <c r="W83">
-        <v>0.2207026573607637</v>
+        <v>0.2208867712953885</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3201302510440275</v>
+        <v>0.3162262235922709</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2248959951122757</v>
+        <v>0.2267959951122757</v>
       </c>
       <c r="C84">
-        <v>-569.7290826561727</v>
+        <v>-581.3769613073142</v>
       </c>
       <c r="D84">
-        <v>182.9849173438274</v>
+        <v>181.0640386926859</v>
       </c>
       <c r="E84">
-        <v>464.5140000000001</v>
+        <v>474.2410000000001</v>
       </c>
       <c r="F84">
-        <v>797.6140000000001</v>
+        <v>807.3410000000001</v>
       </c>
       <c r="G84">
         <v>44.9</v>
@@ -8309,37 +8309,37 @@
         <v>59.475</v>
       </c>
       <c r="M84">
-        <v>188.0773812</v>
+        <v>190.3710078</v>
       </c>
       <c r="N84">
-        <v>-128.6023812000001</v>
+        <v>-130.8960078</v>
       </c>
       <c r="O84">
-        <v>-25.72047624000001</v>
+        <v>-26.17920156000001</v>
       </c>
       <c r="P84">
-        <v>-102.88190496</v>
+        <v>-104.71680624</v>
       </c>
       <c r="Q84">
-        <v>-67.98190496000004</v>
+        <v>-69.81680624000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2431602369447617</v>
+        <v>0.2547696626473948</v>
       </c>
       <c r="T84">
-        <v>3.743850765722673</v>
+        <v>3.964077281353419</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0632452447184542</v>
+        <v>0.06248325381823187</v>
       </c>
       <c r="W84">
-        <v>0.2208867712953885</v>
+        <v>0.2210664487496609</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3162262235922709</v>
+        <v>0.3124162690911593</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2267959951122757</v>
+        <v>0.2286959951122757</v>
       </c>
       <c r="C85">
-        <v>-581.3769613073142</v>
+        <v>-592.9849301787481</v>
       </c>
       <c r="D85">
-        <v>181.0640386926859</v>
+        <v>179.183069821252</v>
       </c>
       <c r="E85">
-        <v>474.2410000000001</v>
+        <v>483.9680000000001</v>
       </c>
       <c r="F85">
-        <v>807.3410000000001</v>
+        <v>817.0680000000001</v>
       </c>
       <c r="G85">
         <v>44.9</v>
@@ -8391,37 +8391,37 @@
         <v>59.475</v>
       </c>
       <c r="M85">
-        <v>190.3710078</v>
+        <v>192.6646344</v>
       </c>
       <c r="N85">
-        <v>-130.8960078</v>
+        <v>-133.1896344</v>
       </c>
       <c r="O85">
-        <v>-26.17920156000001</v>
+        <v>-26.63792688000001</v>
       </c>
       <c r="P85">
-        <v>-104.71680624</v>
+        <v>-106.55170752</v>
       </c>
       <c r="Q85">
-        <v>-69.81680624000003</v>
+        <v>-71.65170752000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2547696626473948</v>
+        <v>0.267830266562857</v>
       </c>
       <c r="T85">
-        <v>3.964077281353419</v>
+        <v>4.211832111438008</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06248325381823187</v>
+        <v>0.06173940555849101</v>
       </c>
       <c r="W85">
-        <v>0.2210664487496609</v>
+        <v>0.2212418481693078</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3124162690911593</v>
+        <v>0.308697027792455</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2286959951122757</v>
+        <v>0.2305959951122757</v>
       </c>
       <c r="C86">
-        <v>-592.9849301787478</v>
+        <v>-604.554220280617</v>
       </c>
       <c r="D86">
-        <v>179.1830698212521</v>
+        <v>177.3407797193831</v>
       </c>
       <c r="E86">
-        <v>483.968</v>
+        <v>493.6950000000001</v>
       </c>
       <c r="F86">
-        <v>817.068</v>
+        <v>826.7950000000001</v>
       </c>
       <c r="G86">
         <v>44.9</v>
@@ -8473,37 +8473,37 @@
         <v>59.475</v>
       </c>
       <c r="M86">
-        <v>192.6646344</v>
+        <v>194.958261</v>
       </c>
       <c r="N86">
-        <v>-133.1896344</v>
+        <v>-135.483261</v>
       </c>
       <c r="O86">
-        <v>-26.63792688000001</v>
+        <v>-27.09665220000001</v>
       </c>
       <c r="P86">
-        <v>-106.55170752</v>
+        <v>-108.3866088</v>
       </c>
       <c r="Q86">
-        <v>-71.65170752</v>
+        <v>-73.48660880000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2678302665628569</v>
+        <v>0.282632284333714</v>
       </c>
       <c r="T86">
-        <v>4.211832111438006</v>
+        <v>4.492620918867206</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06173940555849101</v>
+        <v>0.06101305961074406</v>
       </c>
       <c r="W86">
-        <v>0.2212418481693078</v>
+        <v>0.2214131205437866</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.308697027792455</v>
+        <v>0.3050652980537203</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2305959951122757</v>
+        <v>0.2324959951122757</v>
       </c>
       <c r="C87">
-        <v>-604.554220280617</v>
+        <v>-616.0860125112387</v>
       </c>
       <c r="D87">
-        <v>177.3407797193831</v>
+        <v>175.5359874887614</v>
       </c>
       <c r="E87">
-        <v>493.6950000000001</v>
+        <v>503.422</v>
       </c>
       <c r="F87">
-        <v>826.7950000000001</v>
+        <v>836.522</v>
       </c>
       <c r="G87">
         <v>44.9</v>
@@ -8555,37 +8555,37 @@
         <v>59.475</v>
       </c>
       <c r="M87">
-        <v>194.958261</v>
+        <v>197.2518876</v>
       </c>
       <c r="N87">
-        <v>-135.483261</v>
+        <v>-137.7768876</v>
       </c>
       <c r="O87">
-        <v>-27.09665220000001</v>
+        <v>-27.55537752000001</v>
       </c>
       <c r="P87">
-        <v>-108.3866088</v>
+        <v>-110.22151008</v>
       </c>
       <c r="Q87">
-        <v>-73.48660880000003</v>
+        <v>-75.32151008000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.282632284333714</v>
+        <v>0.2995488760718364</v>
       </c>
       <c r="T87">
-        <v>4.492620918867206</v>
+        <v>4.813522413072007</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06101305961074406</v>
+        <v>0.06030360542922378</v>
       </c>
       <c r="W87">
-        <v>0.2214131205437866</v>
+        <v>0.221580409839789</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3050652980537203</v>
+        <v>0.3015180271461189</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2324959951122757</v>
+        <v>0.2343959951122757</v>
       </c>
       <c r="C88">
-        <v>-616.0860125112387</v>
+        <v>-627.5814401813495</v>
       </c>
       <c r="D88">
-        <v>175.5359874887614</v>
+        <v>173.7675598186504</v>
       </c>
       <c r="E88">
-        <v>503.422</v>
+        <v>513.149</v>
       </c>
       <c r="F88">
-        <v>836.522</v>
+        <v>846.249</v>
       </c>
       <c r="G88">
         <v>44.9</v>
@@ -8637,37 +8637,37 @@
         <v>59.475</v>
       </c>
       <c r="M88">
-        <v>197.2518876</v>
+        <v>199.5455142</v>
       </c>
       <c r="N88">
-        <v>-137.7768876</v>
+        <v>-140.0705142</v>
       </c>
       <c r="O88">
-        <v>-27.55537752000001</v>
+        <v>-28.01410284000001</v>
       </c>
       <c r="P88">
-        <v>-110.22151008</v>
+        <v>-112.05641136</v>
       </c>
       <c r="Q88">
-        <v>-75.32151008000002</v>
+        <v>-77.15641136000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2995488760718364</v>
+        <v>0.3190680203850546</v>
       </c>
       <c r="T88">
-        <v>4.813522413072007</v>
+        <v>5.183793367923699</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06030360542922378</v>
+        <v>0.0596104605392327</v>
       </c>
       <c r="W88">
-        <v>0.221580409839789</v>
+        <v>0.221743853404849</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3015180271461189</v>
+        <v>0.2980523026961635</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2343959951122757</v>
+        <v>0.2362959951122757</v>
       </c>
       <c r="C89">
-        <v>-627.5814401813495</v>
+        <v>-639.0415913872887</v>
       </c>
       <c r="D89">
-        <v>173.7675598186504</v>
+        <v>172.0344086127113</v>
       </c>
       <c r="E89">
-        <v>513.149</v>
+        <v>522.876</v>
       </c>
       <c r="F89">
-        <v>846.249</v>
+        <v>855.976</v>
       </c>
       <c r="G89">
         <v>44.9</v>
@@ -8719,37 +8719,37 @@
         <v>59.475</v>
       </c>
       <c r="M89">
-        <v>199.5455142</v>
+        <v>201.8391408</v>
       </c>
       <c r="N89">
-        <v>-140.0705142</v>
+        <v>-142.3641408</v>
       </c>
       <c r="O89">
-        <v>-28.01410284000001</v>
+        <v>-28.47282816</v>
       </c>
       <c r="P89">
-        <v>-112.05641136</v>
+        <v>-113.89131264</v>
       </c>
       <c r="Q89">
-        <v>-77.15641136000002</v>
+        <v>-78.99131263999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3190680203850546</v>
+        <v>0.3418403554171426</v>
       </c>
       <c r="T89">
-        <v>5.183793367923699</v>
+        <v>5.615776148584009</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0596104605392327</v>
+        <v>0.05893306894219598</v>
       </c>
       <c r="W89">
-        <v>0.221743853404849</v>
+        <v>0.2219035823434302</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2980523026961635</v>
+        <v>0.2946653447109798</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2362959951122757</v>
+        <v>0.2381959951122757</v>
       </c>
       <c r="C90">
-        <v>-639.0415913872887</v>
+        <v>-650.4675112435643</v>
       </c>
       <c r="D90">
-        <v>172.0344086127113</v>
+        <v>170.3354887564357</v>
       </c>
       <c r="E90">
-        <v>522.876</v>
+        <v>532.6030000000001</v>
       </c>
       <c r="F90">
-        <v>855.976</v>
+        <v>865.7030000000001</v>
       </c>
       <c r="G90">
         <v>44.9</v>
@@ -8801,37 +8801,37 @@
         <v>59.475</v>
       </c>
       <c r="M90">
-        <v>201.8391408</v>
+        <v>204.1327674</v>
       </c>
       <c r="N90">
-        <v>-142.3641408</v>
+        <v>-144.6577674</v>
       </c>
       <c r="O90">
-        <v>-28.47282816</v>
+        <v>-28.93155348000001</v>
       </c>
       <c r="P90">
-        <v>-113.89131264</v>
+        <v>-115.72621392</v>
       </c>
       <c r="Q90">
-        <v>-78.99131263999999</v>
+        <v>-80.82621392000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3418403554171426</v>
+        <v>0.3687531150005192</v>
       </c>
       <c r="T90">
-        <v>5.615776148584009</v>
+        <v>6.126301253000737</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05893306894219598</v>
+        <v>0.05827089962823871</v>
       </c>
       <c r="W90">
-        <v>0.2219035823434302</v>
+        <v>0.2220597218676613</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2946653447109798</v>
+        <v>0.2913544981411935</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2381959951122757</v>
+        <v>0.2400959951122757</v>
       </c>
       <c r="C91">
-        <v>-650.4675112435643</v>
+        <v>-661.8602039844272</v>
       </c>
       <c r="D91">
-        <v>170.3354887564357</v>
+        <v>168.6697960155728</v>
       </c>
       <c r="E91">
-        <v>532.6030000000001</v>
+        <v>542.33</v>
       </c>
       <c r="F91">
-        <v>865.7030000000001</v>
+        <v>875.4300000000001</v>
       </c>
       <c r="G91">
         <v>44.9</v>
@@ -8883,37 +8883,37 @@
         <v>59.475</v>
       </c>
       <c r="M91">
-        <v>204.1327674</v>
+        <v>206.426394</v>
       </c>
       <c r="N91">
-        <v>-144.6577674</v>
+        <v>-146.951394</v>
       </c>
       <c r="O91">
-        <v>-28.93155348000001</v>
+        <v>-29.3902788</v>
       </c>
       <c r="P91">
-        <v>-115.72621392</v>
+        <v>-117.5611152</v>
       </c>
       <c r="Q91">
-        <v>-80.82621392000004</v>
+        <v>-82.66111520000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3687531150005192</v>
+        <v>0.4010484265005712</v>
       </c>
       <c r="T91">
-        <v>6.126301253000737</v>
+        <v>6.738931378300811</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05827089962823871</v>
+        <v>0.05762344518792495</v>
       </c>
       <c r="W91">
-        <v>0.2220597218676613</v>
+        <v>0.2222123916246873</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2913544981411935</v>
+        <v>0.2881172259396247</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2400959951122757</v>
+        <v>0.2419959951122757</v>
       </c>
       <c r="C92">
-        <v>-661.8602039844272</v>
+        <v>-673.2206349433325</v>
       </c>
       <c r="D92">
-        <v>168.6697960155728</v>
+        <v>167.0363650566676</v>
       </c>
       <c r="E92">
-        <v>542.33</v>
+        <v>552.057</v>
       </c>
       <c r="F92">
-        <v>875.4300000000001</v>
+        <v>885.157</v>
       </c>
       <c r="G92">
         <v>44.9</v>
@@ -8965,37 +8965,37 @@
         <v>59.475</v>
       </c>
       <c r="M92">
-        <v>206.426394</v>
+        <v>208.7200206</v>
       </c>
       <c r="N92">
-        <v>-146.951394</v>
+        <v>-149.2450206</v>
       </c>
       <c r="O92">
-        <v>-29.3902788</v>
+        <v>-29.84900412000001</v>
       </c>
       <c r="P92">
-        <v>-117.5611152</v>
+        <v>-119.39601648</v>
       </c>
       <c r="Q92">
-        <v>-82.66111520000001</v>
+        <v>-84.49601648000004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4010484265005712</v>
+        <v>0.4405204738895235</v>
       </c>
       <c r="T92">
-        <v>6.738931378300811</v>
+        <v>7.487701531445346</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05762344518792495</v>
+        <v>0.05699022051553017</v>
       </c>
       <c r="W92">
-        <v>0.2222123916246873</v>
+        <v>0.222361706002438</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2881172259396247</v>
+        <v>0.2849511025776508</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2419959951122757</v>
+        <v>0.2438959951122757</v>
       </c>
       <c r="C93">
-        <v>-673.2206349433325</v>
+        <v>-684.5497324184872</v>
       </c>
       <c r="D93">
-        <v>167.0363650566676</v>
+        <v>165.4342675815129</v>
       </c>
       <c r="E93">
-        <v>552.057</v>
+        <v>561.7840000000001</v>
       </c>
       <c r="F93">
-        <v>885.157</v>
+        <v>894.8840000000001</v>
       </c>
       <c r="G93">
         <v>44.9</v>
@@ -9047,37 +9047,37 @@
         <v>59.475</v>
       </c>
       <c r="M93">
-        <v>208.7200206</v>
+        <v>211.0136472</v>
       </c>
       <c r="N93">
-        <v>-149.2450206</v>
+        <v>-151.5386472</v>
       </c>
       <c r="O93">
-        <v>-29.84900412000001</v>
+        <v>-30.30772944000001</v>
       </c>
       <c r="P93">
-        <v>-119.39601648</v>
+        <v>-121.23091776</v>
       </c>
       <c r="Q93">
-        <v>-84.49601648000004</v>
+        <v>-86.33091776000003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4405204738895235</v>
+        <v>0.489860533125714</v>
       </c>
       <c r="T93">
-        <v>7.487701531445346</v>
+        <v>8.423664222876017</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05699022051553017</v>
+        <v>0.0563707615968831</v>
       </c>
       <c r="W93">
-        <v>0.222361706002438</v>
+        <v>0.222507774415455</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2849511025776508</v>
+        <v>0.2818538079844154</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2438959951122757</v>
+        <v>0.2457959951122757</v>
       </c>
       <c r="C94">
-        <v>-684.5497324184872</v>
+        <v>-695.8483894320611</v>
       </c>
       <c r="D94">
-        <v>165.4342675815129</v>
+        <v>163.862610567939</v>
       </c>
       <c r="E94">
-        <v>561.7840000000001</v>
+        <v>571.5110000000001</v>
       </c>
       <c r="F94">
-        <v>894.8840000000001</v>
+        <v>904.6110000000001</v>
       </c>
       <c r="G94">
         <v>44.9</v>
@@ -9129,37 +9129,37 @@
         <v>59.475</v>
       </c>
       <c r="M94">
-        <v>211.0136472</v>
+        <v>213.3072738</v>
       </c>
       <c r="N94">
-        <v>-151.5386472</v>
+        <v>-153.8322738000001</v>
       </c>
       <c r="O94">
-        <v>-30.30772944000001</v>
+        <v>-30.76645476000001</v>
       </c>
       <c r="P94">
-        <v>-121.23091776</v>
+        <v>-123.06581904</v>
       </c>
       <c r="Q94">
-        <v>-86.33091776000003</v>
+        <v>-88.16581904000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.489860533125714</v>
+        <v>0.5532977521436733</v>
       </c>
       <c r="T94">
-        <v>8.423664222876017</v>
+        <v>9.62704482614402</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0563707615968831</v>
+        <v>0.05576462437541124</v>
       </c>
       <c r="W94">
-        <v>0.222507774415455</v>
+        <v>0.2226507015722781</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2818538079844154</v>
+        <v>0.2788231218770562</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2457959951122757</v>
+        <v>0.2476959951122757</v>
       </c>
       <c r="C95">
-        <v>-695.8483894320611</v>
+        <v>-707.1174653900608</v>
       </c>
       <c r="D95">
-        <v>163.862610567939</v>
+        <v>162.3205346099393</v>
       </c>
       <c r="E95">
-        <v>571.5110000000001</v>
+        <v>581.2380000000001</v>
       </c>
       <c r="F95">
-        <v>904.6110000000001</v>
+        <v>914.3380000000001</v>
       </c>
       <c r="G95">
         <v>44.9</v>
@@ -9211,37 +9211,37 @@
         <v>59.475</v>
       </c>
       <c r="M95">
-        <v>213.3072738</v>
+        <v>215.6009004</v>
       </c>
       <c r="N95">
-        <v>-153.8322738000001</v>
+        <v>-156.1259004</v>
       </c>
       <c r="O95">
-        <v>-30.76645476000001</v>
+        <v>-31.22518008000001</v>
       </c>
       <c r="P95">
-        <v>-123.06581904</v>
+        <v>-124.90072032</v>
       </c>
       <c r="Q95">
-        <v>-88.16581904000003</v>
+        <v>-90.00072032000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5532977521436733</v>
+        <v>0.6378807108342857</v>
       </c>
       <c r="T95">
-        <v>9.62704482614402</v>
+        <v>11.23155229716803</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05576462437541124</v>
+        <v>0.05517138369056643</v>
       </c>
       <c r="W95">
-        <v>0.2226507015722781</v>
+        <v>0.2227905877257645</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2788231218770562</v>
+        <v>0.2758569184528321</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2476959951122757</v>
+        <v>0.2495959951122757</v>
       </c>
       <c r="C96">
-        <v>-707.1174653900608</v>
+        <v>-718.3577876493572</v>
       </c>
       <c r="D96">
-        <v>162.3205346099393</v>
+        <v>160.8072123506428</v>
       </c>
       <c r="E96">
-        <v>581.2380000000001</v>
+        <v>590.965</v>
       </c>
       <c r="F96">
-        <v>914.3380000000001</v>
+        <v>924.0650000000001</v>
       </c>
       <c r="G96">
         <v>44.9</v>
@@ -9293,37 +9293,37 @@
         <v>59.475</v>
       </c>
       <c r="M96">
-        <v>215.6009004</v>
+        <v>217.894527</v>
       </c>
       <c r="N96">
-        <v>-156.1259004</v>
+        <v>-158.419527</v>
       </c>
       <c r="O96">
-        <v>-31.22518008000001</v>
+        <v>-31.6839054</v>
       </c>
       <c r="P96">
-        <v>-124.90072032</v>
+        <v>-126.7356216</v>
       </c>
       <c r="Q96">
-        <v>-90.00072032000003</v>
+        <v>-91.83562160000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6378807108342857</v>
+        <v>0.7562968530011431</v>
       </c>
       <c r="T96">
-        <v>11.23155229716803</v>
+        <v>13.47786275660164</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05517138369056643</v>
+        <v>0.05459063228329733</v>
       </c>
       <c r="W96">
-        <v>0.2227905877257645</v>
+        <v>0.2229275289075985</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2758569184528321</v>
+        <v>0.2729531614164866</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2495959951122757</v>
+        <v>0.2514959951122757</v>
       </c>
       <c r="C97">
-        <v>-718.3577876493572</v>
+        <v>-729.5701529978633</v>
       </c>
       <c r="D97">
-        <v>160.8072123506428</v>
+        <v>159.3218470021368</v>
       </c>
       <c r="E97">
-        <v>590.965</v>
+        <v>600.6920000000001</v>
       </c>
       <c r="F97">
-        <v>924.0650000000001</v>
+        <v>933.7920000000001</v>
       </c>
       <c r="G97">
         <v>44.9</v>
@@ -9375,37 +9375,37 @@
         <v>59.475</v>
       </c>
       <c r="M97">
-        <v>217.894527</v>
+        <v>220.1881536</v>
       </c>
       <c r="N97">
-        <v>-158.419527</v>
+        <v>-160.7131536000001</v>
       </c>
       <c r="O97">
-        <v>-31.6839054</v>
+        <v>-32.14263072000001</v>
       </c>
       <c r="P97">
-        <v>-126.7356216</v>
+        <v>-128.5705228800001</v>
       </c>
       <c r="Q97">
-        <v>-91.83562160000002</v>
+        <v>-93.67052288000005</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7562968530011431</v>
+        <v>0.9339210662514292</v>
       </c>
       <c r="T97">
-        <v>13.47786275660164</v>
+        <v>16.84732844575205</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05459063228329733</v>
+        <v>0.05402197986367963</v>
       </c>
       <c r="W97">
-        <v>0.2229275289075985</v>
+        <v>0.2230616171481443</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2729531614164866</v>
+        <v>0.2701098993183981</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2514959951122757</v>
+        <v>0.2533959951122757</v>
       </c>
       <c r="C98">
-        <v>-729.570152997863</v>
+        <v>-740.7553290534289</v>
       </c>
       <c r="D98">
-        <v>159.3218470021369</v>
+        <v>157.8636709465711</v>
       </c>
       <c r="E98">
-        <v>600.692</v>
+        <v>610.419</v>
       </c>
       <c r="F98">
-        <v>933.792</v>
+        <v>943.519</v>
       </c>
       <c r="G98">
         <v>44.9</v>
@@ -9457,37 +9457,37 @@
         <v>59.475</v>
       </c>
       <c r="M98">
-        <v>220.1881536</v>
+        <v>222.4817802</v>
       </c>
       <c r="N98">
-        <v>-160.7131536</v>
+        <v>-163.0067802</v>
       </c>
       <c r="O98">
-        <v>-32.14263072000001</v>
+        <v>-32.60135604000001</v>
       </c>
       <c r="P98">
-        <v>-128.57052288</v>
+        <v>-130.40542416</v>
       </c>
       <c r="Q98">
-        <v>-93.67052288000002</v>
+        <v>-95.50542415999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9339210662514268</v>
+        <v>1.229961421668569</v>
       </c>
       <c r="T98">
-        <v>16.84732844575201</v>
+        <v>22.46310459433601</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05402197986367964</v>
+        <v>0.05346505223621903</v>
       </c>
       <c r="W98">
-        <v>0.2230616171481443</v>
+        <v>0.2231929406826996</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2701098993183981</v>
+        <v>0.2673252611810951</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2533959951122757</v>
+        <v>0.2552959951122757</v>
       </c>
       <c r="C99">
-        <v>-740.7553290534289</v>
+        <v>-751.9140555866149</v>
       </c>
       <c r="D99">
-        <v>157.8636709465711</v>
+        <v>156.431944413385</v>
       </c>
       <c r="E99">
-        <v>610.419</v>
+        <v>620.146</v>
       </c>
       <c r="F99">
-        <v>943.519</v>
+        <v>953.246</v>
       </c>
       <c r="G99">
         <v>44.9</v>
@@ -9539,37 +9539,37 @@
         <v>59.475</v>
       </c>
       <c r="M99">
-        <v>222.4817802</v>
+        <v>224.7754068</v>
       </c>
       <c r="N99">
-        <v>-163.0067802</v>
+        <v>-165.3004068</v>
       </c>
       <c r="O99">
-        <v>-32.60135604000001</v>
+        <v>-33.06008136000001</v>
       </c>
       <c r="P99">
-        <v>-130.40542416</v>
+        <v>-132.24032544</v>
       </c>
       <c r="Q99">
-        <v>-95.50542415999999</v>
+        <v>-97.34032544000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.229961421668569</v>
+        <v>1.822042132502854</v>
       </c>
       <c r="T99">
-        <v>22.46310459433601</v>
+        <v>33.69465689150402</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05346505223621903</v>
+        <v>0.05291949047870659</v>
       </c>
       <c r="W99">
-        <v>0.2231929406826996</v>
+        <v>0.223321584145121</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2673252611810951</v>
+        <v>0.2645974523935329</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2552959951122757</v>
+        <v>0.2571959951122756</v>
       </c>
       <c r="C100">
-        <v>-751.9140555866149</v>
+        <v>-763.0470457721319</v>
       </c>
       <c r="D100">
-        <v>156.431944413385</v>
+        <v>155.0259542278682</v>
       </c>
       <c r="E100">
-        <v>620.146</v>
+        <v>629.873</v>
       </c>
       <c r="F100">
-        <v>953.246</v>
+        <v>962.9730000000001</v>
       </c>
       <c r="G100">
         <v>44.9</v>
@@ -9621,37 +9621,37 @@
         <v>59.475</v>
       </c>
       <c r="M100">
-        <v>224.7754068</v>
+        <v>227.0690334</v>
       </c>
       <c r="N100">
-        <v>-165.3004068</v>
+        <v>-167.5940334</v>
       </c>
       <c r="O100">
-        <v>-33.06008136000001</v>
+        <v>-33.51880668</v>
       </c>
       <c r="P100">
-        <v>-132.24032544</v>
+        <v>-134.07522672</v>
       </c>
       <c r="Q100">
-        <v>-97.34032544000002</v>
+        <v>-99.17522672000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.822042132502854</v>
+        <v>3.598284265005707</v>
       </c>
       <c r="T100">
-        <v>33.69465689150402</v>
+        <v>67.38931378300803</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05291949047870659</v>
+        <v>0.05238495017084086</v>
       </c>
       <c r="W100">
-        <v>0.223321584145121</v>
+        <v>0.2234476287497157</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2645974523935329</v>
+        <v>0.2619247508542043</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2571959951122756</v>
-      </c>
-      <c r="C101">
-        <v>-763.0470457721319</v>
-      </c>
-      <c r="D101">
-        <v>155.0259542278682</v>
-      </c>
-      <c r="E101">
-        <v>629.873</v>
-      </c>
-      <c r="F101">
-        <v>962.9730000000001</v>
-      </c>
-      <c r="G101">
-        <v>44.9</v>
-      </c>
-      <c r="H101">
-        <v>639.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>94.375</v>
-      </c>
-      <c r="K101">
-        <v>34.9</v>
-      </c>
-      <c r="L101">
-        <v>59.475</v>
-      </c>
-      <c r="M101">
-        <v>227.0690334</v>
-      </c>
-      <c r="N101">
-        <v>-167.5940334</v>
-      </c>
-      <c r="O101">
-        <v>-33.51880668</v>
-      </c>
-      <c r="P101">
-        <v>-134.07522672</v>
-      </c>
-      <c r="Q101">
-        <v>-99.17522672000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.598284265005707</v>
-      </c>
-      <c r="T101">
-        <v>67.38931378300803</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05238495017084086</v>
-      </c>
-      <c r="W101">
-        <v>0.2234476287497157</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2619247508542043</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
